--- a/research/traditional_assets/database/data/turks_caicos_islands/turks_caicos_islands_restaurant_dining.xlsx
+++ b/research/traditional_assets/database/data/turks_caicos_islands/turks_caicos_islands_restaurant_dining.xlsx
@@ -588,25 +588,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0984</v>
+        <v>0.0504</v>
+      </c>
+      <c r="E2">
+        <v>0.112</v>
       </c>
       <c r="G2">
-        <v>-0.07376237623762376</v>
+        <v>0.1506544502617801</v>
       </c>
       <c r="H2">
-        <v>-0.07772277227722772</v>
+        <v>0.1505235602094241</v>
       </c>
       <c r="I2">
-        <v>-0.04232673267326733</v>
+        <v>0.1308900523560209</v>
       </c>
       <c r="J2">
-        <v>-0.04232673267326733</v>
+        <v>0.1308900523560209</v>
       </c>
       <c r="K2">
-        <v>-0.233</v>
+        <v>1.81</v>
       </c>
       <c r="L2">
-        <v>-0.05767326732673268</v>
+        <v>0.2369109947643979</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +627,76 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.033</v>
+        <v>0.049</v>
       </c>
       <c r="V2">
-        <v>0.003495762711864407</v>
+        <v>0.00580568720379147</v>
       </c>
       <c r="W2">
-        <v>-0.08859315589353613</v>
+        <v>0.7541666666666668</v>
       </c>
       <c r="X2">
-        <v>0.1132626286981665</v>
+        <v>0.09924394500691956</v>
       </c>
       <c r="Y2">
-        <v>-0.2018557845917027</v>
+        <v>0.6549227216597472</v>
       </c>
       <c r="Z2">
-        <v>1.54434250764526</v>
+        <v>2.86464191976003</v>
       </c>
       <c r="AA2">
-        <v>-0.06536697247706422</v>
+        <v>0.3749531308586427</v>
       </c>
       <c r="AB2">
-        <v>0.1121875312484839</v>
+        <v>0.09860148696778429</v>
       </c>
       <c r="AC2">
-        <v>-0.1775545037255482</v>
+        <v>0.2763516438908584</v>
       </c>
       <c r="AD2">
-        <v>0.3</v>
+        <v>0.267</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.3</v>
+        <v>0.267</v>
       </c>
       <c r="AG2">
-        <v>0.267</v>
+        <v>0.218</v>
       </c>
       <c r="AH2">
-        <v>0.03080082135523614</v>
+        <v>0.03066498219823131</v>
       </c>
       <c r="AI2">
-        <v>0.1111111111111111</v>
+        <v>0.05977165883143049</v>
       </c>
       <c r="AJ2">
-        <v>0.0275059235603173</v>
+        <v>0.02517902517902518</v>
       </c>
       <c r="AK2">
-        <v>0.1001124859392576</v>
+        <v>0.04934359438660028</v>
       </c>
       <c r="AL2">
-        <v>0.036</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.036</v>
+        <v>-0.002</v>
       </c>
       <c r="AN2">
-        <v>3.409090909090909</v>
-      </c>
-      <c r="AO2">
-        <v>-4.750000000000001</v>
+        <v>0.2102362204724409</v>
       </c>
       <c r="AP2">
-        <v>3.03409090909091</v>
+        <v>0.1716535433070866</v>
       </c>
       <c r="AQ2">
-        <v>-4.750000000000001</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0984</v>
+        <v>0.0504</v>
+      </c>
+      <c r="E3">
+        <v>0.112</v>
       </c>
       <c r="G3">
-        <v>-0.07376237623762376</v>
+        <v>0.1506544502617801</v>
       </c>
       <c r="H3">
-        <v>-0.07772277227722772</v>
+        <v>0.1505235602094241</v>
       </c>
       <c r="I3">
-        <v>-0.04232673267326733</v>
+        <v>0.1308900523560209</v>
       </c>
       <c r="J3">
-        <v>-0.04232673267326733</v>
+        <v>0.1308900523560209</v>
       </c>
       <c r="K3">
-        <v>-0.233</v>
+        <v>1.81</v>
       </c>
       <c r="L3">
-        <v>-0.05767326732673268</v>
+        <v>0.2369109947643979</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +746,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +755,76 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.033</v>
+        <v>0.049</v>
       </c>
       <c r="V3">
-        <v>0.003495762711864407</v>
+        <v>0.00580568720379147</v>
       </c>
       <c r="W3">
-        <v>-0.08859315589353613</v>
+        <v>0.7541666666666668</v>
       </c>
       <c r="X3">
-        <v>0.1132626286981665</v>
+        <v>0.09924394500691956</v>
       </c>
       <c r="Y3">
-        <v>-0.2018557845917027</v>
+        <v>0.6549227216597472</v>
       </c>
       <c r="Z3">
-        <v>1.54434250764526</v>
+        <v>2.86464191976003</v>
       </c>
       <c r="AA3">
-        <v>-0.06536697247706422</v>
+        <v>0.3749531308586427</v>
       </c>
       <c r="AB3">
-        <v>0.1121875312484839</v>
+        <v>0.09860148696778429</v>
       </c>
       <c r="AC3">
-        <v>-0.1775545037255482</v>
+        <v>0.2763516438908584</v>
       </c>
       <c r="AD3">
-        <v>0.3</v>
+        <v>0.267</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.3</v>
+        <v>0.267</v>
       </c>
       <c r="AG3">
-        <v>0.267</v>
+        <v>0.218</v>
       </c>
       <c r="AH3">
-        <v>0.03080082135523614</v>
+        <v>0.03066498219823131</v>
       </c>
       <c r="AI3">
-        <v>0.1111111111111111</v>
+        <v>0.05977165883143049</v>
       </c>
       <c r="AJ3">
-        <v>0.0275059235603173</v>
+        <v>0.02517902517902518</v>
       </c>
       <c r="AK3">
-        <v>0.1001124859392576</v>
+        <v>0.04934359438660028</v>
       </c>
       <c r="AL3">
-        <v>0.036</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.036</v>
+        <v>-0.002</v>
       </c>
       <c r="AN3">
-        <v>3.409090909090909</v>
-      </c>
-      <c r="AO3">
-        <v>-4.750000000000001</v>
+        <v>0.2102362204724409</v>
       </c>
       <c r="AP3">
-        <v>3.03409090909091</v>
+        <v>0.1716535433070866</v>
       </c>
       <c r="AQ3">
-        <v>-4.750000000000001</v>
+        <v>-500</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/turks_caicos_islands/turks_caicos_islands_restaurant_dining.xlsx
+++ b/research/traditional_assets/database/data/turks_caicos_islands/turks_caicos_islands_restaurant_dining.xlsx
@@ -1127,43 +1127,43 @@
         <v>44.0526315789474</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>348.631029661128</v>
       </c>
       <c r="G2">
         <v>0.182075471698113</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0450283018867924</v>
       </c>
       <c r="I2">
         <v>0.0404357846218311</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>4.58</v>
       </c>
       <c r="L2">
-        <v>4.80663741577858</v>
+        <v>4.75780305910477</v>
       </c>
       <c r="M2">
         <v>4.711</v>
       </c>
       <c r="N2">
-        <v>4.74463741577858</v>
+        <v>4.74353305910477</v>
       </c>
       <c r="O2">
         <v>0.193</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.04773</v>
       </c>
       <c r="Q2">
         <v>0.10177194211703</v>
       </c>
       <c r="R2">
-        <v>0.100391829251121</v>
+        <v>0.100436829251121</v>
       </c>
       <c r="S2">
         <v>0.0799309777667576</v>
@@ -1185,13 +1185,13 @@
         <v>0.102692314632227</v>
       </c>
       <c r="X2">
-        <v>0.100391829251121</v>
+        <v>0.100943261869819</v>
       </c>
       <c r="Y2">
         <v>0.880106013436312</v>
       </c>
       <c r="Z2">
-        <v>0.844518236232622</v>
+        <v>0.853048723467295</v>
       </c>
       <c r="AA2">
         <v>0.193</v>
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1003918292511212</v>
+        <v>0.1004368292511212</v>
       </c>
       <c r="C2">
-        <v>4.806637415778581</v>
+        <v>4.757803059104767</v>
       </c>
       <c r="D2">
-        <v>4.74463741577858</v>
+        <v>4.743533059104767</v>
       </c>
       <c r="E2">
-        <v>-0.193</v>
+        <v>-0.14527</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.04772999999999999</v>
       </c>
       <c r="G2">
         <v>0.062</v>
@@ -1445,28 +1445,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.002400819</v>
       </c>
       <c r="N2">
-        <v>0.8370000000000001</v>
+        <v>0.8345991810000001</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>0.8370000000000001</v>
+        <v>0.8345991810000001</v>
       </c>
       <c r="Q2">
-        <v>1.06</v>
+        <v>1.057599181</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1003918292511212</v>
+        <v>0.1009432618698193</v>
       </c>
       <c r="T2">
-        <v>0.8445182362326223</v>
+        <v>0.8530487234672953</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>348.6310296611282</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1004368292511212</v>
+        <v>0.1004818292511211</v>
       </c>
       <c r="C3">
-        <v>4.757803059104767</v>
+        <v>4.70896921640905</v>
       </c>
       <c r="D3">
-        <v>4.743533059104767</v>
+        <v>4.74242921640905</v>
       </c>
       <c r="E3">
-        <v>-0.14527</v>
+        <v>-0.09754000000000002</v>
       </c>
       <c r="F3">
-        <v>0.04772999999999999</v>
+        <v>0.09545999999999999</v>
       </c>
       <c r="G3">
         <v>0.062</v>
@@ -1527,28 +1527,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M3">
-        <v>0.002400819</v>
+        <v>0.004801638</v>
       </c>
       <c r="N3">
-        <v>0.8345991810000001</v>
+        <v>0.8321983620000001</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0.8345991810000001</v>
+        <v>0.8321983620000001</v>
       </c>
       <c r="Q3">
-        <v>1.057599181</v>
+        <v>1.055198362</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1009432618698193</v>
+        <v>0.1015059482154297</v>
       </c>
       <c r="T3">
-        <v>0.8530487234672953</v>
+        <v>0.861753302278186</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>348.6310296611282</v>
+        <v>174.3155148305641</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1004818292511211</v>
+        <v>0.1005268292511211</v>
       </c>
       <c r="C4">
-        <v>4.70896921640905</v>
+        <v>4.6601358873327</v>
       </c>
       <c r="D4">
-        <v>4.74242921640905</v>
+        <v>4.7413258873327</v>
       </c>
       <c r="E4">
-        <v>-0.09754000000000002</v>
+        <v>-0.04981000000000002</v>
       </c>
       <c r="F4">
-        <v>0.09545999999999999</v>
+        <v>0.14319</v>
       </c>
       <c r="G4">
         <v>0.062</v>
@@ -1609,28 +1609,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M4">
-        <v>0.004801638</v>
+        <v>0.007202456999999999</v>
       </c>
       <c r="N4">
-        <v>0.8321983620000001</v>
+        <v>0.8297975430000001</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>0.8321983620000001</v>
+        <v>0.8297975430000001</v>
       </c>
       <c r="Q4">
-        <v>1.055198362</v>
+        <v>1.052797543</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1015059482154297</v>
+        <v>0.102080236341362</v>
       </c>
       <c r="T4">
-        <v>0.861753302278186</v>
+        <v>0.8706373569408477</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>174.3155148305641</v>
+        <v>116.2103432203761</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1005268292511211</v>
+        <v>0.1005718292511212</v>
       </c>
       <c r="C5">
-        <v>4.6601358873327</v>
+        <v>4.611303071517314</v>
       </c>
       <c r="D5">
-        <v>4.7413258873327</v>
+        <v>4.740223071517314</v>
       </c>
       <c r="E5">
-        <v>-0.04981000000000002</v>
+        <v>-0.002080000000000026</v>
       </c>
       <c r="F5">
-        <v>0.14319</v>
+        <v>0.19092</v>
       </c>
       <c r="G5">
         <v>0.062</v>
@@ -1691,28 +1691,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M5">
-        <v>0.007202456999999999</v>
+        <v>0.009603275999999999</v>
       </c>
       <c r="N5">
-        <v>0.8297975430000001</v>
+        <v>0.8273967240000001</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>0.8297975430000001</v>
+        <v>0.8273967240000001</v>
       </c>
       <c r="Q5">
-        <v>1.052797543</v>
+        <v>1.050396724</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.102080236341362</v>
+        <v>0.1026664888032512</v>
       </c>
       <c r="T5">
-        <v>0.8706373569408477</v>
+        <v>0.8797064960756483</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>116.2103432203761</v>
+        <v>87.15775741528205</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1005718292511212</v>
+        <v>0.1006168292511211</v>
       </c>
       <c r="C6">
-        <v>4.611303071517314</v>
+        <v>4.562470768604833</v>
       </c>
       <c r="D6">
-        <v>4.740223071517314</v>
+        <v>4.739120768604833</v>
       </c>
       <c r="E6">
-        <v>-0.002080000000000026</v>
+        <v>0.04565</v>
       </c>
       <c r="F6">
-        <v>0.19092</v>
+        <v>0.23865</v>
       </c>
       <c r="G6">
         <v>0.062</v>
@@ -1773,28 +1773,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M6">
-        <v>0.009603275999999999</v>
+        <v>0.012004095</v>
       </c>
       <c r="N6">
-        <v>0.8273967240000001</v>
+        <v>0.8249959050000001</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>0.8273967240000001</v>
+        <v>0.8249959050000001</v>
       </c>
       <c r="Q6">
-        <v>1.050396724</v>
+        <v>1.047995905</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1026664888032512</v>
+        <v>0.1032650834222328</v>
       </c>
       <c r="T6">
-        <v>0.8797064960756483</v>
+        <v>0.8889665644553919</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>87.15775741528205</v>
+        <v>69.72620593222564</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1006168292511211</v>
+        <v>0.1006618292511212</v>
       </c>
       <c r="C7">
-        <v>4.562470768604833</v>
+        <v>4.513638978237521</v>
       </c>
       <c r="D7">
-        <v>4.739120768604833</v>
+        <v>4.738018978237521</v>
       </c>
       <c r="E7">
-        <v>0.04565</v>
+        <v>0.09338000000000002</v>
       </c>
       <c r="F7">
-        <v>0.23865</v>
+        <v>0.28638</v>
       </c>
       <c r="G7">
         <v>0.062</v>
@@ -1855,28 +1855,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M7">
-        <v>0.012004095</v>
+        <v>0.014404914</v>
       </c>
       <c r="N7">
-        <v>0.8249959050000001</v>
+        <v>0.8225950860000001</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>0.8249959050000001</v>
+        <v>0.8225950860000001</v>
       </c>
       <c r="Q7">
-        <v>1.047995905</v>
+        <v>1.045595086</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1032650834222328</v>
+        <v>0.1038764140969374</v>
       </c>
       <c r="T7">
-        <v>0.8889665644553919</v>
+        <v>0.8984236555666195</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>69.72620593222564</v>
+        <v>58.10517161018802</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1006618292511212</v>
+        <v>0.1007068292511212</v>
       </c>
       <c r="C8">
-        <v>4.513638978237521</v>
+        <v>4.46480770005798</v>
       </c>
       <c r="D8">
-        <v>4.738018978237521</v>
+        <v>4.73691770005798</v>
       </c>
       <c r="E8">
-        <v>0.09337999999999996</v>
+        <v>0.14111</v>
       </c>
       <c r="F8">
-        <v>0.28638</v>
+        <v>0.33411</v>
       </c>
       <c r="G8">
         <v>0.062</v>
@@ -1937,28 +1937,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M8">
-        <v>0.014404914</v>
+        <v>0.016805733</v>
       </c>
       <c r="N8">
-        <v>0.8225950860000001</v>
+        <v>0.8201942670000001</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>0.8225950860000001</v>
+        <v>0.8201942670000001</v>
       </c>
       <c r="Q8">
-        <v>1.045595086</v>
+        <v>1.043194267</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1038764140969374</v>
+        <v>0.1045008916678722</v>
       </c>
       <c r="T8">
-        <v>0.8984236555666195</v>
+        <v>0.9080841249813143</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>58.10517161018804</v>
+        <v>49.80443280873261</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1007068292511211</v>
+        <v>0.1007518292511212</v>
       </c>
       <c r="C9">
-        <v>4.46480770005798</v>
+        <v>4.415976933709144</v>
       </c>
       <c r="D9">
-        <v>4.73691770005798</v>
+        <v>4.735816933709144</v>
       </c>
       <c r="E9">
-        <v>0.14111</v>
+        <v>0.18884</v>
       </c>
       <c r="F9">
-        <v>0.33411</v>
+        <v>0.38184</v>
       </c>
       <c r="G9">
         <v>0.062</v>
@@ -2019,28 +2019,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M9">
-        <v>0.016805733</v>
+        <v>0.019206552</v>
       </c>
       <c r="N9">
-        <v>0.8201942670000001</v>
+        <v>0.8177934480000001</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>0.8201942670000001</v>
+        <v>0.8177934480000001</v>
       </c>
       <c r="Q9">
-        <v>1.043194267</v>
+        <v>1.040793448</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1045008916678722</v>
+        <v>0.1051389448381752</v>
       </c>
       <c r="T9">
-        <v>0.9080841249813143</v>
+        <v>0.9179546046006765</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>49.8044328087326</v>
+        <v>43.57887870764102</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1007518292511212</v>
+        <v>0.1007968292511212</v>
       </c>
       <c r="C10">
-        <v>4.415976933709144</v>
+        <v>4.367146678834276</v>
       </c>
       <c r="D10">
-        <v>4.735816933709144</v>
+        <v>4.734716678834276</v>
       </c>
       <c r="E10">
-        <v>0.18884</v>
+        <v>0.2365699999999999</v>
       </c>
       <c r="F10">
-        <v>0.38184</v>
+        <v>0.42957</v>
       </c>
       <c r="G10">
         <v>0.062</v>
@@ -2101,28 +2101,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M10">
-        <v>0.019206552</v>
+        <v>0.021607371</v>
       </c>
       <c r="N10">
-        <v>0.8177934480000001</v>
+        <v>0.8153926290000001</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>0.8177934480000001</v>
+        <v>0.8153926290000001</v>
       </c>
       <c r="Q10">
-        <v>1.040793448</v>
+        <v>1.038392629</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1051389448381752</v>
+        <v>0.1057910211550782</v>
       </c>
       <c r="T10">
-        <v>0.9179546046006765</v>
+        <v>0.9280420178380466</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>43.57887870764102</v>
+        <v>38.73678107345869</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1007968292511212</v>
+        <v>0.1008418292511211</v>
       </c>
       <c r="C11">
-        <v>4.367146678834276</v>
+        <v>4.318316935076973</v>
       </c>
       <c r="D11">
-        <v>4.734716678834276</v>
+        <v>4.733616935076973</v>
       </c>
       <c r="E11">
-        <v>0.2365699999999999</v>
+        <v>0.2842999999999999</v>
       </c>
       <c r="F11">
-        <v>0.42957</v>
+        <v>0.4772999999999999</v>
       </c>
       <c r="G11">
         <v>0.062</v>
@@ -2183,28 +2183,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M11">
-        <v>0.021607371</v>
+        <v>0.02400819</v>
       </c>
       <c r="N11">
-        <v>0.8153926290000001</v>
+        <v>0.8129918100000001</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>0.8153926290000001</v>
+        <v>0.8129918100000001</v>
       </c>
       <c r="Q11">
-        <v>1.038392629</v>
+        <v>1.03599181</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1057910211550782</v>
+        <v>0.1064575880568013</v>
       </c>
       <c r="T11">
-        <v>0.9280420178380466</v>
+        <v>0.9383535958140249</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>38.73678107345869</v>
+        <v>34.86310296611283</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1008418292511211</v>
+        <v>0.1008868292511212</v>
       </c>
       <c r="C12">
-        <v>4.318316935076973</v>
+        <v>4.269487702081163</v>
       </c>
       <c r="D12">
-        <v>4.733616935076973</v>
+        <v>4.732517702081163</v>
       </c>
       <c r="E12">
-        <v>0.2843</v>
+        <v>0.33203</v>
       </c>
       <c r="F12">
-        <v>0.4773</v>
+        <v>0.52503</v>
       </c>
       <c r="G12">
         <v>0.062</v>
@@ -2265,28 +2265,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M12">
-        <v>0.02400819</v>
+        <v>0.026409009</v>
       </c>
       <c r="N12">
-        <v>0.8129918100000001</v>
+        <v>0.8105909910000001</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>0.8129918100000001</v>
+        <v>0.8105909910000001</v>
       </c>
       <c r="Q12">
-        <v>1.03599181</v>
+        <v>1.033590991</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1064575880568013</v>
+        <v>0.1071391339900238</v>
       </c>
       <c r="T12">
-        <v>0.9383535958140249</v>
+        <v>0.948896894643396</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>34.86310296611282</v>
+        <v>31.69372996919347</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1008868292511212</v>
+        <v>0.1009318292511212</v>
       </c>
       <c r="C13">
-        <v>4.269487702081163</v>
+        <v>4.220658979491103</v>
       </c>
       <c r="D13">
-        <v>4.732517702081163</v>
+        <v>4.731418979491102</v>
       </c>
       <c r="E13">
-        <v>0.33203</v>
+        <v>0.3797599999999999</v>
       </c>
       <c r="F13">
-        <v>0.52503</v>
+        <v>0.5727599999999999</v>
       </c>
       <c r="G13">
         <v>0.062</v>
@@ -2347,28 +2347,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M13">
-        <v>0.026409009</v>
+        <v>0.028809828</v>
       </c>
       <c r="N13">
-        <v>0.8105909910000001</v>
+        <v>0.8081901720000001</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>0.8105909910000001</v>
+        <v>0.8081901720000001</v>
       </c>
       <c r="Q13">
-        <v>1.033590991</v>
+        <v>1.031190172</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1071391339900238</v>
+        <v>0.1078361696035468</v>
       </c>
       <c r="T13">
-        <v>0.948896894643396</v>
+        <v>0.9596798139007071</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>31.69372996919347</v>
+        <v>29.05258580509402</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1009318292511212</v>
+        <v>0.1009768292511212</v>
       </c>
       <c r="C14">
-        <v>4.220658979491103</v>
+        <v>4.171830766951381</v>
       </c>
       <c r="D14">
-        <v>4.731418979491102</v>
+        <v>4.730320766951381</v>
       </c>
       <c r="E14">
-        <v>0.3797599999999999</v>
+        <v>0.42749</v>
       </c>
       <c r="F14">
-        <v>0.5727599999999999</v>
+        <v>0.62049</v>
       </c>
       <c r="G14">
         <v>0.062</v>
@@ -2429,28 +2429,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M14">
-        <v>0.028809828</v>
+        <v>0.031210647</v>
       </c>
       <c r="N14">
-        <v>0.8081901720000001</v>
+        <v>0.8057893530000001</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>0.8081901720000001</v>
+        <v>0.8057893530000001</v>
       </c>
       <c r="Q14">
-        <v>1.031190172</v>
+        <v>1.028789353</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1078361696035468</v>
+        <v>0.1085492290242772</v>
       </c>
       <c r="T14">
-        <v>0.9596798139007071</v>
+        <v>0.970710616359336</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>29.05258580509402</v>
+        <v>26.81777151239448</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1009768292511212</v>
+        <v>0.1010218292511212</v>
       </c>
       <c r="C15">
-        <v>4.171830766951381</v>
+        <v>4.123003064106917</v>
       </c>
       <c r="D15">
-        <v>4.730320766951381</v>
+        <v>4.729223064106916</v>
       </c>
       <c r="E15">
-        <v>0.42749</v>
+        <v>0.47522</v>
       </c>
       <c r="F15">
-        <v>0.62049</v>
+        <v>0.66822</v>
       </c>
       <c r="G15">
         <v>0.062</v>
@@ -2511,28 +2511,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M15">
-        <v>0.031210647</v>
+        <v>0.033611466</v>
       </c>
       <c r="N15">
-        <v>0.8057893530000001</v>
+        <v>0.8033885340000001</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>0.8057893530000001</v>
+        <v>0.8033885340000001</v>
       </c>
       <c r="Q15">
-        <v>1.028789353</v>
+        <v>1.026388534</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1085492290242772</v>
+        <v>0.1092788712222339</v>
       </c>
       <c r="T15">
-        <v>0.970710616359336</v>
+        <v>0.9819979491077004</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>26.81777151239448</v>
+        <v>24.9022164043663</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1010218292511212</v>
+        <v>0.1010668292511212</v>
       </c>
       <c r="C16">
-        <v>4.123003064106917</v>
+        <v>4.074175870602955</v>
       </c>
       <c r="D16">
-        <v>4.729223064106916</v>
+        <v>4.728125870602955</v>
       </c>
       <c r="E16">
-        <v>0.47522</v>
+        <v>0.52295</v>
       </c>
       <c r="F16">
-        <v>0.66822</v>
+        <v>0.7159500000000001</v>
       </c>
       <c r="G16">
         <v>0.062</v>
@@ -2593,28 +2593,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M16">
-        <v>0.033611466</v>
+        <v>0.036012285</v>
       </c>
       <c r="N16">
-        <v>0.8033885340000001</v>
+        <v>0.8009877150000001</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>0.8033885340000001</v>
+        <v>0.8009877150000001</v>
       </c>
       <c r="Q16">
-        <v>1.026388534</v>
+        <v>1.023987715</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1092788712222339</v>
+        <v>0.1100256814719072</v>
       </c>
       <c r="T16">
-        <v>0.9819979491077004</v>
+        <v>0.9935508661560263</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>24.9022164043663</v>
+        <v>23.24206864407521</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1010668292511212</v>
+        <v>0.1011118292511211</v>
       </c>
       <c r="C17">
-        <v>4.074175870602955</v>
+        <v>4.025349186085077</v>
       </c>
       <c r="D17">
-        <v>4.728125870602955</v>
+        <v>4.727029186085077</v>
       </c>
       <c r="E17">
-        <v>0.52295</v>
+        <v>0.5706799999999999</v>
       </c>
       <c r="F17">
-        <v>0.71595</v>
+        <v>0.7636799999999999</v>
       </c>
       <c r="G17">
         <v>0.062</v>
@@ -2675,28 +2675,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M17">
-        <v>0.036012285</v>
+        <v>0.038413104</v>
       </c>
       <c r="N17">
-        <v>0.8009877150000001</v>
+        <v>0.7985868960000001</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>0.8009877150000001</v>
+        <v>0.7985868960000001</v>
       </c>
       <c r="Q17">
-        <v>1.023987715</v>
+        <v>1.021586896</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1100256814719072</v>
+        <v>0.1107902729180014</v>
       </c>
       <c r="T17">
-        <v>0.9935508661560263</v>
+        <v>1.005378852657884</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>23.24206864407521</v>
+        <v>21.78943935382051</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1011118292511211</v>
+        <v>0.1011568292511211</v>
       </c>
       <c r="C18">
-        <v>4.025349186085077</v>
+        <v>3.976523010199184</v>
       </c>
       <c r="D18">
-        <v>4.727029186085077</v>
+        <v>4.725933010199184</v>
       </c>
       <c r="E18">
-        <v>0.5706799999999999</v>
+        <v>0.6184099999999999</v>
       </c>
       <c r="F18">
-        <v>0.7636799999999999</v>
+        <v>0.81141</v>
       </c>
       <c r="G18">
         <v>0.062</v>
@@ -2757,28 +2757,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M18">
-        <v>0.038413104</v>
+        <v>0.040813923</v>
       </c>
       <c r="N18">
-        <v>0.7985868960000001</v>
+        <v>0.7961860770000001</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>0.7985868960000001</v>
+        <v>0.7961860770000001</v>
       </c>
       <c r="Q18">
-        <v>1.021586896</v>
+        <v>1.019186077</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1107902729180014</v>
+        <v>0.1115732882543628</v>
       </c>
       <c r="T18">
-        <v>1.005378852657884</v>
+        <v>1.017491850882678</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>21.78943935382051</v>
+        <v>20.50770762712519</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1011568292511211</v>
+        <v>0.1012018292511212</v>
       </c>
       <c r="C19">
-        <v>3.976523010199184</v>
+        <v>3.927697342591512</v>
       </c>
       <c r="D19">
-        <v>4.725933010199184</v>
+        <v>4.724837342591512</v>
       </c>
       <c r="E19">
-        <v>0.6184099999999999</v>
+        <v>0.66614</v>
       </c>
       <c r="F19">
-        <v>0.81141</v>
+        <v>0.85914</v>
       </c>
       <c r="G19">
         <v>0.062</v>
@@ -2839,28 +2839,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M19">
-        <v>0.040813923</v>
+        <v>0.043214742</v>
       </c>
       <c r="N19">
-        <v>0.7961860770000001</v>
+        <v>0.7937852580000001</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>0.7961860770000001</v>
+        <v>0.7937852580000001</v>
       </c>
       <c r="Q19">
-        <v>1.019186077</v>
+        <v>1.016785258</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1115732882543628</v>
+        <v>0.1123754015257575</v>
       </c>
       <c r="T19">
-        <v>1.017491850882678</v>
+        <v>1.029900288088564</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>20.50770762712519</v>
+        <v>19.36839053672934</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1012018292511212</v>
+        <v>0.1012468292511211</v>
       </c>
       <c r="C20">
-        <v>3.927697342591511</v>
+        <v>3.878872182908621</v>
       </c>
       <c r="D20">
-        <v>4.724837342591511</v>
+        <v>4.723742182908621</v>
       </c>
       <c r="E20">
-        <v>0.66614</v>
+        <v>0.71387</v>
       </c>
       <c r="F20">
-        <v>0.8591399999999999</v>
+        <v>0.90687</v>
       </c>
       <c r="G20">
         <v>0.062</v>
@@ -2921,28 +2921,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M20">
-        <v>0.04321474199999999</v>
+        <v>0.04561556099999999</v>
       </c>
       <c r="N20">
-        <v>0.7937852580000001</v>
+        <v>0.7913844390000001</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>0.7937852580000001</v>
+        <v>0.7913844390000001</v>
       </c>
       <c r="Q20">
-        <v>1.016785258</v>
+        <v>1.014384439</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1123754015257575</v>
+        <v>0.1131973200631125</v>
       </c>
       <c r="T20">
-        <v>1.029900288088564</v>
+        <v>1.042615106460028</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>19.36839053672935</v>
+        <v>18.34900156111201</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1012468292511211</v>
+        <v>0.1012918292511212</v>
       </c>
       <c r="C21">
-        <v>3.878872182908621</v>
+        <v>3.830047530797405</v>
       </c>
       <c r="D21">
-        <v>4.723742182908621</v>
+        <v>4.722647530797405</v>
       </c>
       <c r="E21">
-        <v>0.71387</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="F21">
-        <v>0.90687</v>
+        <v>0.9546</v>
       </c>
       <c r="G21">
         <v>0.062</v>
@@ -3003,28 +3003,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M21">
-        <v>0.04561556099999999</v>
+        <v>0.04801638</v>
       </c>
       <c r="N21">
-        <v>0.7913844390000001</v>
+        <v>0.7889836200000001</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>0.7913844390000001</v>
+        <v>0.7889836200000001</v>
       </c>
       <c r="Q21">
-        <v>1.014384439</v>
+        <v>1.01198362</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1131973200631125</v>
+        <v>0.1140397865639014</v>
       </c>
       <c r="T21">
-        <v>1.042615106460028</v>
+        <v>1.055647795290778</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>18.34900156111201</v>
+        <v>17.43155148305641</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1012918292511212</v>
+        <v>0.1013368292511212</v>
       </c>
       <c r="C22">
-        <v>3.830047530797405</v>
+        <v>3.781223385905076</v>
       </c>
       <c r="D22">
-        <v>4.722647530797405</v>
+        <v>4.721553385905075</v>
       </c>
       <c r="E22">
-        <v>0.7616000000000001</v>
+        <v>0.8093299999999999</v>
       </c>
       <c r="F22">
-        <v>0.9546</v>
+        <v>1.00233</v>
       </c>
       <c r="G22">
         <v>0.062</v>
@@ -3085,28 +3085,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M22">
-        <v>0.04801638</v>
+        <v>0.050417199</v>
       </c>
       <c r="N22">
-        <v>0.7889836200000001</v>
+        <v>0.7865828010000001</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>0.7889836200000001</v>
+        <v>0.7865828010000001</v>
       </c>
       <c r="Q22">
-        <v>1.01198362</v>
+        <v>1.009582801</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1140397865639014</v>
+        <v>0.1149035813305331</v>
       </c>
       <c r="T22">
-        <v>1.055647795290778</v>
+        <v>1.069010425610915</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>17.43155148305641</v>
+        <v>16.60147760291087</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1013368292511212</v>
+        <v>0.1013818292511212</v>
       </c>
       <c r="C23">
-        <v>3.781223385905076</v>
+        <v>3.732399747879178</v>
       </c>
       <c r="D23">
-        <v>4.721553385905075</v>
+        <v>4.720459747879178</v>
       </c>
       <c r="E23">
-        <v>0.8093299999999999</v>
+        <v>0.8570599999999999</v>
       </c>
       <c r="F23">
-        <v>1.00233</v>
+        <v>1.05006</v>
       </c>
       <c r="G23">
         <v>0.062</v>
@@ -3167,28 +3167,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M23">
-        <v>0.050417199</v>
+        <v>0.05281801799999999</v>
       </c>
       <c r="N23">
-        <v>0.7865828010000001</v>
+        <v>0.7841819820000001</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>0.7865828010000001</v>
+        <v>0.7841819820000001</v>
       </c>
       <c r="Q23">
-        <v>1.009582801</v>
+        <v>1.007181982</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1149035813305331</v>
+        <v>0.1157895246809245</v>
       </c>
       <c r="T23">
-        <v>1.069010425610915</v>
+        <v>1.082715687477721</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>16.60147760291087</v>
+        <v>15.84686498459674</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1013818292511212</v>
+        <v>0.1014268292511212</v>
       </c>
       <c r="C24">
-        <v>3.732399747879178</v>
+        <v>3.683576616367584</v>
       </c>
       <c r="D24">
-        <v>4.720459747879178</v>
+        <v>4.719366616367584</v>
       </c>
       <c r="E24">
-        <v>0.8570599999999999</v>
+        <v>0.90479</v>
       </c>
       <c r="F24">
-        <v>1.05006</v>
+        <v>1.09779</v>
       </c>
       <c r="G24">
         <v>0.062</v>
@@ -3249,28 +3249,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M24">
-        <v>0.05281801799999999</v>
+        <v>0.055218837</v>
       </c>
       <c r="N24">
-        <v>0.7841819820000001</v>
+        <v>0.7817811630000001</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>0.7841819820000001</v>
+        <v>0.7817811630000001</v>
       </c>
       <c r="Q24">
-        <v>1.007181982</v>
+        <v>1.004781163</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1157895246809245</v>
+        <v>0.1166984795469106</v>
       </c>
       <c r="T24">
-        <v>1.082715687477721</v>
+        <v>1.096776930172237</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>15.84686498459674</v>
+        <v>15.15787085483166</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1014268292511212</v>
+        <v>0.1014718292511212</v>
       </c>
       <c r="C25">
-        <v>3.683576616367584</v>
+        <v>3.634753991018489</v>
       </c>
       <c r="D25">
-        <v>4.719366616367584</v>
+        <v>4.718273991018489</v>
       </c>
       <c r="E25">
-        <v>0.90479</v>
+        <v>0.95252</v>
       </c>
       <c r="F25">
-        <v>1.09779</v>
+        <v>1.14552</v>
       </c>
       <c r="G25">
         <v>0.062</v>
@@ -3331,28 +3331,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M25">
-        <v>0.055218837</v>
+        <v>0.05761965600000001</v>
       </c>
       <c r="N25">
-        <v>0.7817811630000001</v>
+        <v>0.7793803440000001</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>0.7817811630000001</v>
+        <v>0.7793803440000001</v>
       </c>
       <c r="Q25">
-        <v>1.004781163</v>
+        <v>1.002380344</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1166984795469106</v>
+        <v>0.117631354277791</v>
       </c>
       <c r="T25">
-        <v>1.096776930172237</v>
+        <v>1.11120820556924</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>15.15787085483166</v>
+        <v>14.52629290254701</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1014718292511212</v>
+        <v>0.1015168292511212</v>
       </c>
       <c r="C26">
-        <v>3.634753991018489</v>
+        <v>3.585931871480414</v>
       </c>
       <c r="D26">
-        <v>4.718273991018489</v>
+        <v>4.717181871480414</v>
       </c>
       <c r="E26">
-        <v>0.9525199999999998</v>
+        <v>1.00025</v>
       </c>
       <c r="F26">
-        <v>1.14552</v>
+        <v>1.19325</v>
       </c>
       <c r="G26">
         <v>0.062</v>
@@ -3413,28 +3413,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M26">
-        <v>0.05761965599999999</v>
+        <v>0.06002047499999999</v>
       </c>
       <c r="N26">
-        <v>0.7793803440000001</v>
+        <v>0.7769795250000001</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>0.7793803440000001</v>
+        <v>0.7769795250000001</v>
       </c>
       <c r="Q26">
-        <v>1.002380344</v>
+        <v>0.9999795250000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.117631354277791</v>
+        <v>0.1185891056681615</v>
       </c>
       <c r="T26">
-        <v>1.11120820556924</v>
+        <v>1.12602431497683</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>14.52629290254701</v>
+        <v>13.94524118644513</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1015168292511212</v>
+        <v>0.1015618292511212</v>
       </c>
       <c r="C27">
-        <v>3.585931871480414</v>
+        <v>3.537110257402208</v>
       </c>
       <c r="D27">
-        <v>4.717181871480414</v>
+        <v>4.716090257402207</v>
       </c>
       <c r="E27">
-        <v>1.00025</v>
+        <v>1.04798</v>
       </c>
       <c r="F27">
-        <v>1.19325</v>
+        <v>1.24098</v>
       </c>
       <c r="G27">
         <v>0.062</v>
@@ -3495,28 +3495,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M27">
-        <v>0.06002047499999999</v>
+        <v>0.062421294</v>
       </c>
       <c r="N27">
-        <v>0.7769795250000001</v>
+        <v>0.7745787060000001</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>0.7769795250000001</v>
+        <v>0.7745787060000001</v>
       </c>
       <c r="Q27">
-        <v>0.9999795250000001</v>
+        <v>0.9975787060000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1185891056681615</v>
+        <v>0.1195727422312448</v>
       </c>
       <c r="T27">
-        <v>1.12602431497683</v>
+        <v>1.141240859773814</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>13.94524118644513</v>
+        <v>13.40888575619724</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1015618292511212</v>
+        <v>0.1016068292511212</v>
       </c>
       <c r="C28">
-        <v>3.537110257402208</v>
+        <v>3.488289148433042</v>
       </c>
       <c r="D28">
-        <v>4.716090257402207</v>
+        <v>4.714999148433042</v>
       </c>
       <c r="E28">
-        <v>1.04798</v>
+        <v>1.09571</v>
       </c>
       <c r="F28">
-        <v>1.24098</v>
+        <v>1.28871</v>
       </c>
       <c r="G28">
         <v>0.062</v>
@@ -3577,28 +3577,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M28">
-        <v>0.062421294</v>
+        <v>0.064822113</v>
       </c>
       <c r="N28">
-        <v>0.7745787060000001</v>
+        <v>0.7721778870000001</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>0.7745787060000001</v>
+        <v>0.7721778870000001</v>
       </c>
       <c r="Q28">
-        <v>0.9975787060000001</v>
+        <v>0.9951778870000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1195727422312448</v>
+        <v>0.1205833277412619</v>
       </c>
       <c r="T28">
-        <v>1.141240859773814</v>
+        <v>1.156874296209072</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>13.40888575619724</v>
+        <v>12.91226035781956</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1016068292511212</v>
+        <v>0.1020718292511212</v>
       </c>
       <c r="C29">
-        <v>3.488289148433042</v>
+        <v>3.429313848497813</v>
       </c>
       <c r="D29">
-        <v>4.714999148433042</v>
+        <v>4.703753848497813</v>
       </c>
       <c r="E29">
-        <v>1.09571</v>
+        <v>1.14344</v>
       </c>
       <c r="F29">
-        <v>1.28871</v>
+        <v>1.33644</v>
       </c>
       <c r="G29">
         <v>0.062</v>
@@ -3659,45 +3659,45 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M29">
-        <v>0.064822113</v>
+        <v>0.069227592</v>
       </c>
       <c r="N29">
-        <v>0.7721778870000001</v>
+        <v>0.7677724080000001</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>0.7721778870000001</v>
+        <v>0.7677724080000001</v>
       </c>
       <c r="Q29">
-        <v>0.9951778870000001</v>
+        <v>0.9907724080000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1205833277412619</v>
+        <v>0.1216219850710016</v>
       </c>
       <c r="T29">
-        <v>1.156874296209072</v>
+        <v>1.172941994767531</v>
       </c>
       <c r="U29">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V29">
         <v>0</v>
       </c>
       <c r="W29">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y29">
-        <v>12.91226035781956</v>
+        <v>12.0905548758651</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1020718292511212</v>
+        <v>0.1021318292511212</v>
       </c>
       <c r="C30">
-        <v>3.429313848497813</v>
+        <v>3.380136748047786</v>
       </c>
       <c r="D30">
-        <v>4.703753848497813</v>
+        <v>4.702306748047786</v>
       </c>
       <c r="E30">
-        <v>1.14344</v>
+        <v>1.19117</v>
       </c>
       <c r="F30">
-        <v>1.33644</v>
+        <v>1.38417</v>
       </c>
       <c r="G30">
         <v>0.062</v>
@@ -3741,28 +3741,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M30">
-        <v>0.069227592</v>
+        <v>0.07170000600000001</v>
       </c>
       <c r="N30">
-        <v>0.7677724080000001</v>
+        <v>0.765299994</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>0.7677724080000001</v>
+        <v>0.765299994</v>
       </c>
       <c r="Q30">
-        <v>0.9907724080000001</v>
+        <v>0.988299994</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1216219850710016</v>
+        <v>0.1226899003536918</v>
       </c>
       <c r="T30">
-        <v>1.172941994767531</v>
+        <v>1.189462304552989</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>12.0905548758651</v>
+        <v>11.67363919049044</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1021318292511211</v>
+        <v>0.1021918292511211</v>
       </c>
       <c r="C31">
-        <v>3.380136748047786</v>
+        <v>3.330960537719024</v>
       </c>
       <c r="D31">
-        <v>4.702306748047786</v>
+        <v>4.700860537719024</v>
       </c>
       <c r="E31">
-        <v>1.19117</v>
+        <v>1.2389</v>
       </c>
       <c r="F31">
-        <v>1.38417</v>
+        <v>1.4319</v>
       </c>
       <c r="G31">
         <v>0.062</v>
@@ -3823,28 +3823,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M31">
-        <v>0.071700006</v>
+        <v>0.07417241999999999</v>
       </c>
       <c r="N31">
-        <v>0.765299994</v>
+        <v>0.7628275800000001</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>0.765299994</v>
+        <v>0.7628275800000001</v>
       </c>
       <c r="Q31">
-        <v>0.988299994</v>
+        <v>0.98582758</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1226899003536918</v>
+        <v>0.1237883275016017</v>
       </c>
       <c r="T31">
-        <v>1.189462304552989</v>
+        <v>1.206454623189461</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.67363919049045</v>
+        <v>11.28451788414077</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1021918292511211</v>
+        <v>0.1022518292511212</v>
       </c>
       <c r="C32">
-        <v>3.330960537719024</v>
+        <v>3.2817852166905</v>
       </c>
       <c r="D32">
-        <v>4.700860537719024</v>
+        <v>4.6994152166905</v>
       </c>
       <c r="E32">
-        <v>1.2389</v>
+        <v>1.28663</v>
       </c>
       <c r="F32">
-        <v>1.4319</v>
+        <v>1.47963</v>
       </c>
       <c r="G32">
         <v>0.062</v>
@@ -3905,28 +3905,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M32">
-        <v>0.07417241999999999</v>
+        <v>0.076644834</v>
       </c>
       <c r="N32">
-        <v>0.7628275800000001</v>
+        <v>0.7603551660000001</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>0.7628275800000001</v>
+        <v>0.7603551660000001</v>
       </c>
       <c r="Q32">
-        <v>0.98582758</v>
+        <v>0.9833551660000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1237883275016017</v>
+        <v>0.1249185931175669</v>
       </c>
       <c r="T32">
-        <v>1.206454623189461</v>
+        <v>1.223939472800902</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.28451788414077</v>
+        <v>10.92050117820074</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1022518292511212</v>
+        <v>0.1023118292511211</v>
       </c>
       <c r="C33">
-        <v>3.2817852166905</v>
+        <v>3.232610784142199</v>
       </c>
       <c r="D33">
-        <v>4.6994152166905</v>
+        <v>4.697970784142199</v>
       </c>
       <c r="E33">
-        <v>1.28663</v>
+        <v>1.33436</v>
       </c>
       <c r="F33">
-        <v>1.47963</v>
+        <v>1.52736</v>
       </c>
       <c r="G33">
         <v>0.062</v>
@@ -3987,28 +3987,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M33">
-        <v>0.076644834</v>
+        <v>0.07911724799999999</v>
       </c>
       <c r="N33">
-        <v>0.7603551660000001</v>
+        <v>0.7578827520000001</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>0.7603551660000001</v>
+        <v>0.7578827520000001</v>
       </c>
       <c r="Q33">
-        <v>0.9833551660000001</v>
+        <v>0.9808827520000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1249185931175669</v>
+        <v>0.1260821018398841</v>
       </c>
       <c r="T33">
-        <v>1.223939472800902</v>
+        <v>1.241938582695033</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.92050117820074</v>
+        <v>10.57923551638197</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1023118292511211</v>
+        <v>0.1023718292511211</v>
       </c>
       <c r="C34">
-        <v>3.232610784142199</v>
+        <v>3.183437239255109</v>
       </c>
       <c r="D34">
-        <v>4.697970784142199</v>
+        <v>4.696527239255109</v>
       </c>
       <c r="E34">
-        <v>1.33436</v>
+        <v>1.38209</v>
       </c>
       <c r="F34">
-        <v>1.52736</v>
+        <v>1.57509</v>
       </c>
       <c r="G34">
         <v>0.062</v>
@@ -4069,28 +4069,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M34">
-        <v>0.07911724799999999</v>
+        <v>0.08158966199999999</v>
       </c>
       <c r="N34">
-        <v>0.7578827520000001</v>
+        <v>0.7554103380000001</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>0.7578827520000001</v>
+        <v>0.7554103380000001</v>
       </c>
       <c r="Q34">
-        <v>0.9808827520000001</v>
+        <v>0.9784103380000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1260821018398841</v>
+        <v>0.1272803421658525</v>
       </c>
       <c r="T34">
-        <v>1.241938582695033</v>
+        <v>1.260474979451675</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.57923551638197</v>
+        <v>10.25865262194615</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1023718292511211</v>
+        <v>0.1024318292511212</v>
       </c>
       <c r="C35">
-        <v>3.183437239255109</v>
+        <v>3.134264581211228</v>
       </c>
       <c r="D35">
-        <v>4.696527239255109</v>
+        <v>4.695084581211227</v>
       </c>
       <c r="E35">
-        <v>1.38209</v>
+        <v>1.42982</v>
       </c>
       <c r="F35">
-        <v>1.57509</v>
+        <v>1.62282</v>
       </c>
       <c r="G35">
         <v>0.062</v>
@@ -4151,28 +4151,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M35">
-        <v>0.08158966199999999</v>
+        <v>0.084062076</v>
       </c>
       <c r="N35">
-        <v>0.7554103380000001</v>
+        <v>0.752937924</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>0.7554103380000001</v>
+        <v>0.752937924</v>
       </c>
       <c r="Q35">
-        <v>0.9784103380000001</v>
+        <v>0.975937924</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1272803421658525</v>
+        <v>0.128514892804729</v>
       </c>
       <c r="T35">
-        <v>1.260474979451675</v>
+        <v>1.279573085200943</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>10.25865262194615</v>
+        <v>9.956927544830085</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1024318292511212</v>
+        <v>0.1030868292511212</v>
       </c>
       <c r="C36">
-        <v>3.134264581211228</v>
+        <v>3.070843020961617</v>
       </c>
       <c r="D36">
-        <v>4.695084581211227</v>
+        <v>4.679393020961617</v>
       </c>
       <c r="E36">
-        <v>1.42982</v>
+        <v>1.47755</v>
       </c>
       <c r="F36">
-        <v>1.62282</v>
+        <v>1.67055</v>
       </c>
       <c r="G36">
         <v>0.062</v>
@@ -4233,45 +4233,45 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M36">
-        <v>0.084062076</v>
+        <v>0.08937442499999999</v>
       </c>
       <c r="N36">
-        <v>0.752937924</v>
+        <v>0.747625575</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>0.752937924</v>
+        <v>0.747625575</v>
       </c>
       <c r="Q36">
-        <v>0.975937924</v>
+        <v>0.970625575</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.128514892804729</v>
+        <v>0.1297874296171095</v>
       </c>
       <c r="T36">
-        <v>1.279573085200943</v>
+        <v>1.299258824973265</v>
       </c>
       <c r="U36">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V36">
         <v>0</v>
       </c>
       <c r="W36">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>9.956927544830085</v>
+        <v>9.365095215997195</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1030868292511212</v>
+        <v>0.1031638292511211</v>
       </c>
       <c r="C37">
-        <v>3.070843020961617</v>
+        <v>3.021275251377285</v>
       </c>
       <c r="D37">
-        <v>4.679393020961617</v>
+        <v>4.677555251377285</v>
       </c>
       <c r="E37">
-        <v>1.47755</v>
+        <v>1.52528</v>
       </c>
       <c r="F37">
-        <v>1.67055</v>
+        <v>1.71828</v>
       </c>
       <c r="G37">
         <v>0.062</v>
@@ -4315,28 +4315,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M37">
-        <v>0.08937442499999999</v>
+        <v>0.09192798000000001</v>
       </c>
       <c r="N37">
-        <v>0.747625575</v>
+        <v>0.7450720200000001</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>0.747625575</v>
+        <v>0.7450720200000001</v>
       </c>
       <c r="Q37">
-        <v>0.970625575</v>
+        <v>0.96807202</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1297874296171095</v>
+        <v>0.1310997332048768</v>
       </c>
       <c r="T37">
-        <v>1.299258824973265</v>
+        <v>1.319559744113472</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>9.365095215997195</v>
+        <v>9.104953682219493</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1031638292511212</v>
+        <v>0.1032408292511212</v>
       </c>
       <c r="C38">
-        <v>3.021275251377285</v>
+        <v>2.971708924745543</v>
       </c>
       <c r="D38">
-        <v>4.677555251377285</v>
+        <v>4.675718924745542</v>
       </c>
       <c r="E38">
-        <v>1.52528</v>
+        <v>1.57301</v>
       </c>
       <c r="F38">
-        <v>1.71828</v>
+        <v>1.76601</v>
       </c>
       <c r="G38">
         <v>0.062</v>
@@ -4397,28 +4397,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M38">
-        <v>0.09192797999999999</v>
+        <v>0.09448153499999999</v>
       </c>
       <c r="N38">
-        <v>0.7450720200000001</v>
+        <v>0.7425184650000001</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>0.7450720200000001</v>
+        <v>0.7425184650000001</v>
       </c>
       <c r="Q38">
-        <v>0.96807202</v>
+        <v>0.965518465</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1310997332048768</v>
+        <v>0.1324536972240019</v>
       </c>
       <c r="T38">
-        <v>1.319559744113472</v>
+        <v>1.340505136877179</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>9.104953682219495</v>
+        <v>8.858873852970319</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1032408292511212</v>
+        <v>0.1033178292511212</v>
       </c>
       <c r="C39">
-        <v>2.971708924745543</v>
+        <v>2.922144039367622</v>
       </c>
       <c r="D39">
-        <v>4.675718924745542</v>
+        <v>4.673884039367622</v>
       </c>
       <c r="E39">
-        <v>1.57301</v>
+        <v>1.62074</v>
       </c>
       <c r="F39">
-        <v>1.76601</v>
+        <v>1.81374</v>
       </c>
       <c r="G39">
         <v>0.062</v>
@@ -4479,28 +4479,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M39">
-        <v>0.09448153499999999</v>
+        <v>0.09703508999999999</v>
       </c>
       <c r="N39">
-        <v>0.7425184650000001</v>
+        <v>0.7399649100000001</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>0.7425184650000001</v>
+        <v>0.7399649100000001</v>
       </c>
       <c r="Q39">
-        <v>0.965518465</v>
+        <v>0.9629649100000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1324536972240019</v>
+        <v>0.1338513375018083</v>
       </c>
       <c r="T39">
-        <v>1.340505136877179</v>
+        <v>1.362126187471971</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.858873852970319</v>
+        <v>8.625745593681629</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1033178292511212</v>
+        <v>0.1033948292511211</v>
       </c>
       <c r="C40">
-        <v>2.922144039367622</v>
+        <v>2.872580593547422</v>
       </c>
       <c r="D40">
-        <v>4.673884039367622</v>
+        <v>4.672050593547421</v>
       </c>
       <c r="E40">
-        <v>1.62074</v>
+        <v>1.66847</v>
       </c>
       <c r="F40">
-        <v>1.81374</v>
+        <v>1.86147</v>
       </c>
       <c r="G40">
         <v>0.062</v>
@@ -4561,28 +4561,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M40">
-        <v>0.09703508999999999</v>
+        <v>0.09958864499999999</v>
       </c>
       <c r="N40">
-        <v>0.7399649100000001</v>
+        <v>0.7374113550000001</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>0.7399649100000001</v>
+        <v>0.7374113550000001</v>
       </c>
       <c r="Q40">
-        <v>0.9629649100000001</v>
+        <v>0.9604113550000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1338513375018083</v>
+        <v>0.1352948020510183</v>
       </c>
       <c r="T40">
-        <v>1.362126187471971</v>
+        <v>1.384456124971512</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.625745593681629</v>
+        <v>8.404572629741073</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1033948292511211</v>
+        <v>0.1034718292511212</v>
       </c>
       <c r="C41">
-        <v>2.872580593547422</v>
+        <v>2.8230185855915</v>
       </c>
       <c r="D41">
-        <v>4.672050593547421</v>
+        <v>4.6702185855915</v>
       </c>
       <c r="E41">
-        <v>1.66847</v>
+        <v>1.7162</v>
       </c>
       <c r="F41">
-        <v>1.86147</v>
+        <v>1.9092</v>
       </c>
       <c r="G41">
         <v>0.062</v>
@@ -4643,28 +4643,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M41">
-        <v>0.09958864499999999</v>
+        <v>0.1021422</v>
       </c>
       <c r="N41">
-        <v>0.7374113550000001</v>
+        <v>0.7348578000000001</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>0.7374113550000001</v>
+        <v>0.7348578000000001</v>
       </c>
       <c r="Q41">
-        <v>0.9604113550000001</v>
+        <v>0.9578578000000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1352948020510183</v>
+        <v>0.1367863820852019</v>
       </c>
       <c r="T41">
-        <v>1.384456124971512</v>
+        <v>1.407530393721037</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.404572629741073</v>
+        <v>8.194458313997545</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1034718292511212</v>
+        <v>0.1035488292511211</v>
       </c>
       <c r="C42">
-        <v>2.8230185855915</v>
+        <v>2.773458013809073</v>
       </c>
       <c r="D42">
-        <v>4.6702185855915</v>
+        <v>4.668388013809072</v>
       </c>
       <c r="E42">
-        <v>1.7162</v>
+        <v>1.76393</v>
       </c>
       <c r="F42">
-        <v>1.9092</v>
+        <v>1.95693</v>
       </c>
       <c r="G42">
         <v>0.062</v>
@@ -4725,28 +4725,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M42">
-        <v>0.1021422</v>
+        <v>0.104695755</v>
       </c>
       <c r="N42">
-        <v>0.7348578000000001</v>
+        <v>0.7323042450000001</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>0.7348578000000001</v>
+        <v>0.7323042450000001</v>
       </c>
       <c r="Q42">
-        <v>0.9578578000000001</v>
+        <v>0.9553042450000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1367863820852019</v>
+        <v>0.1383285241544426</v>
       </c>
       <c r="T42">
-        <v>1.407530393721037</v>
+        <v>1.431386841072241</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.194458313997545</v>
+        <v>7.994593477070777</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1035488292511211</v>
+        <v>0.1036258292511212</v>
       </c>
       <c r="C43">
-        <v>2.773458013809073</v>
+        <v>2.723898876512001</v>
       </c>
       <c r="D43">
-        <v>4.668388013809072</v>
+        <v>4.666558876512001</v>
       </c>
       <c r="E43">
-        <v>1.76393</v>
+        <v>1.81166</v>
       </c>
       <c r="F43">
-        <v>1.95693</v>
+        <v>2.00466</v>
       </c>
       <c r="G43">
         <v>0.062</v>
@@ -4807,28 +4807,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M43">
-        <v>0.104695755</v>
+        <v>0.10724931</v>
       </c>
       <c r="N43">
-        <v>0.7323042450000001</v>
+        <v>0.7297506900000001</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>0.7323042450000001</v>
+        <v>0.7297506900000001</v>
       </c>
       <c r="Q43">
-        <v>0.9553042450000001</v>
+        <v>0.9527506900000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1383285241544426</v>
+        <v>0.1399238435364158</v>
       </c>
       <c r="T43">
-        <v>1.431386841072241</v>
+        <v>1.456065924539004</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.994593477070777</v>
+        <v>7.804246013330997</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1036258292511212</v>
+        <v>0.1037028292511212</v>
       </c>
       <c r="C44">
-        <v>2.723898876512001</v>
+        <v>2.674341172014794</v>
       </c>
       <c r="D44">
-        <v>4.666558876512001</v>
+        <v>4.664731172014794</v>
       </c>
       <c r="E44">
-        <v>1.81166</v>
+        <v>1.85939</v>
       </c>
       <c r="F44">
-        <v>2.00466</v>
+        <v>2.05239</v>
       </c>
       <c r="G44">
         <v>0.062</v>
@@ -4889,28 +4889,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M44">
-        <v>0.10724931</v>
+        <v>0.109802865</v>
       </c>
       <c r="N44">
-        <v>0.7297506900000001</v>
+        <v>0.7271971350000001</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>0.7297506900000001</v>
+        <v>0.7271971350000001</v>
       </c>
       <c r="Q44">
-        <v>0.9527506900000001</v>
+        <v>0.950197135</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1399238435364158</v>
+        <v>0.1415751390370547</v>
       </c>
       <c r="T44">
-        <v>1.456065924539004</v>
+        <v>1.481610940758987</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.804246013330997</v>
+        <v>7.622751919997716</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1037028292511212</v>
+        <v>0.1041318292511212</v>
       </c>
       <c r="C45">
-        <v>2.674341172014794</v>
+        <v>2.616454398357874</v>
       </c>
       <c r="D45">
-        <v>4.664731172014794</v>
+        <v>4.654574398357874</v>
       </c>
       <c r="E45">
-        <v>1.85939</v>
+        <v>1.90712</v>
       </c>
       <c r="F45">
-        <v>2.05239</v>
+        <v>2.10012</v>
       </c>
       <c r="G45">
         <v>0.062</v>
@@ -4971,45 +4971,45 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M45">
-        <v>0.109802865</v>
+        <v>0.114036516</v>
       </c>
       <c r="N45">
-        <v>0.7271971350000001</v>
+        <v>0.7229634840000001</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>0.7271971350000001</v>
+        <v>0.7229634840000001</v>
       </c>
       <c r="Q45">
-        <v>0.950197135</v>
+        <v>0.9459634840000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1415751390370547</v>
+        <v>0.1432854093770021</v>
       </c>
       <c r="T45">
-        <v>1.481610940758987</v>
+        <v>1.508068278986826</v>
       </c>
       <c r="U45">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V45">
         <v>0</v>
       </c>
       <c r="W45">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y45">
-        <v>7.622751919997716</v>
+        <v>7.339754223989096</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1041318292511212</v>
+        <v>0.1042168292511212</v>
       </c>
       <c r="C46">
-        <v>2.616454398357874</v>
+        <v>2.566717231649463</v>
       </c>
       <c r="D46">
-        <v>4.654574398357874</v>
+        <v>4.652567231649463</v>
       </c>
       <c r="E46">
-        <v>1.90712</v>
+        <v>1.95485</v>
       </c>
       <c r="F46">
-        <v>2.10012</v>
+        <v>2.14785</v>
       </c>
       <c r="G46">
         <v>0.062</v>
@@ -5053,28 +5053,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M46">
-        <v>0.114036516</v>
+        <v>0.116628255</v>
       </c>
       <c r="N46">
-        <v>0.7229634840000001</v>
+        <v>0.7203717450000001</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>0.7229634840000001</v>
+        <v>0.7203717450000001</v>
       </c>
       <c r="Q46">
-        <v>0.9459634840000001</v>
+        <v>0.9433717450000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1432854093770021</v>
+        <v>0.1450578713656748</v>
       </c>
       <c r="T46">
-        <v>1.508068278986826</v>
+        <v>1.535487702241132</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>7.339754223989096</v>
+        <v>7.176648574567116</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1042168292511212</v>
+        <v>0.1043018292511212</v>
       </c>
       <c r="C47">
-        <v>2.566717231649463</v>
+        <v>2.516981795273975</v>
       </c>
       <c r="D47">
-        <v>4.652567231649463</v>
+        <v>4.650561795273974</v>
       </c>
       <c r="E47">
-        <v>1.95485</v>
+        <v>2.00258</v>
       </c>
       <c r="F47">
-        <v>2.14785</v>
+        <v>2.19558</v>
       </c>
       <c r="G47">
         <v>0.062</v>
@@ -5135,28 +5135,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M47">
-        <v>0.116628255</v>
+        <v>0.119219994</v>
       </c>
       <c r="N47">
-        <v>0.7203717450000001</v>
+        <v>0.717780006</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>0.7203717450000001</v>
+        <v>0.717780006</v>
       </c>
       <c r="Q47">
-        <v>0.9433717450000001</v>
+        <v>0.940780006</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1450578713656748</v>
+        <v>0.1468959800946688</v>
       </c>
       <c r="T47">
-        <v>1.535487702241132</v>
+        <v>1.563922659690041</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.176648574567116</v>
+        <v>7.020634475120003</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1043018292511212</v>
+        <v>0.1043868292511212</v>
       </c>
       <c r="C48">
-        <v>2.516981795273975</v>
+        <v>2.467248086994852</v>
       </c>
       <c r="D48">
-        <v>4.650561795273974</v>
+        <v>4.648558086994852</v>
       </c>
       <c r="E48">
-        <v>2.00258</v>
+        <v>2.05031</v>
       </c>
       <c r="F48">
-        <v>2.19558</v>
+        <v>2.24331</v>
       </c>
       <c r="G48">
         <v>0.062</v>
@@ -5217,28 +5217,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M48">
-        <v>0.119219994</v>
+        <v>0.121811733</v>
       </c>
       <c r="N48">
-        <v>0.717780006</v>
+        <v>0.715188267</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>0.717780006</v>
+        <v>0.715188267</v>
       </c>
       <c r="Q48">
-        <v>0.940780006</v>
+        <v>0.938188267</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1468959800946688</v>
+        <v>0.1488034514172097</v>
       </c>
       <c r="T48">
-        <v>1.563922659690041</v>
+        <v>1.593430634401174</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.020634475120003</v>
+        <v>6.871259273521706</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1043868292511212</v>
+        <v>0.1044718292511212</v>
       </c>
       <c r="C49">
-        <v>2.467248086994852</v>
+        <v>2.417516104579391</v>
       </c>
       <c r="D49">
-        <v>4.648558086994852</v>
+        <v>4.646556104579391</v>
       </c>
       <c r="E49">
-        <v>2.05031</v>
+        <v>2.09804</v>
       </c>
       <c r="F49">
-        <v>2.24331</v>
+        <v>2.29104</v>
       </c>
       <c r="G49">
         <v>0.062</v>
@@ -5299,28 +5299,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M49">
-        <v>0.121811733</v>
+        <v>0.124403472</v>
       </c>
       <c r="N49">
-        <v>0.715188267</v>
+        <v>0.7125965280000001</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>0.715188267</v>
+        <v>0.7125965280000001</v>
       </c>
       <c r="Q49">
-        <v>0.938188267</v>
+        <v>0.935596528</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1488034514172097</v>
+        <v>0.1507842870213869</v>
       </c>
       <c r="T49">
-        <v>1.593430634401174</v>
+        <v>1.624073531216581</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.871259273521706</v>
+        <v>6.728108038656671</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1044718292511212</v>
+        <v>0.1045568292511212</v>
       </c>
       <c r="C50">
-        <v>2.417516104579391</v>
+        <v>2.367785845798732</v>
       </c>
       <c r="D50">
-        <v>4.646556104579391</v>
+        <v>4.644555845798732</v>
       </c>
       <c r="E50">
-        <v>2.09804</v>
+        <v>2.14577</v>
       </c>
       <c r="F50">
-        <v>2.29104</v>
+        <v>2.33877</v>
       </c>
       <c r="G50">
         <v>0.062</v>
@@ -5381,28 +5381,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M50">
-        <v>0.124403472</v>
+        <v>0.126995211</v>
       </c>
       <c r="N50">
-        <v>0.7125965280000001</v>
+        <v>0.7100047890000001</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50">
-        <v>0.7125965280000001</v>
+        <v>0.7100047890000001</v>
       </c>
       <c r="Q50">
-        <v>0.935596528</v>
+        <v>0.9330047890000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1507842870213868</v>
+        <v>0.1528428024531787</v>
       </c>
       <c r="T50">
-        <v>1.624073531216581</v>
+        <v>1.655918110260044</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.728108038656671</v>
+        <v>6.590799711337147</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1045568292511212</v>
+        <v>0.1046418292511211</v>
       </c>
       <c r="C51">
-        <v>2.367785845798732</v>
+        <v>2.318057308427853</v>
       </c>
       <c r="D51">
-        <v>4.644555845798732</v>
+        <v>4.642557308427852</v>
       </c>
       <c r="E51">
-        <v>2.14577</v>
+        <v>2.1935</v>
       </c>
       <c r="F51">
-        <v>2.33877</v>
+        <v>2.3865</v>
       </c>
       <c r="G51">
         <v>0.062</v>
@@ -5463,28 +5463,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M51">
-        <v>0.126995211</v>
+        <v>0.12958695</v>
       </c>
       <c r="N51">
-        <v>0.7100047890000001</v>
+        <v>0.7074130500000001</v>
       </c>
       <c r="O51">
         <v>0</v>
       </c>
       <c r="P51">
-        <v>0.7100047890000001</v>
+        <v>0.7074130500000001</v>
       </c>
       <c r="Q51">
-        <v>0.9330047890000001</v>
+        <v>0.9304130500000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1528428024531787</v>
+        <v>0.1549836585022423</v>
       </c>
       <c r="T51">
-        <v>1.655918110260044</v>
+        <v>1.689036472465245</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.590799711337147</v>
+        <v>6.458983717110404</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1046418292511211</v>
+        <v>0.1047268292511211</v>
       </c>
       <c r="C52">
-        <v>2.318057308427853</v>
+        <v>2.268330490245555</v>
       </c>
       <c r="D52">
-        <v>4.642557308427852</v>
+        <v>4.640560490245554</v>
       </c>
       <c r="E52">
-        <v>2.1935</v>
+        <v>2.24123</v>
       </c>
       <c r="F52">
-        <v>2.3865</v>
+        <v>2.43423</v>
       </c>
       <c r="G52">
         <v>0.062</v>
@@ -5545,28 +5545,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M52">
-        <v>0.12958695</v>
+        <v>0.132178689</v>
       </c>
       <c r="N52">
-        <v>0.7074130500000001</v>
+        <v>0.7048213110000001</v>
       </c>
       <c r="O52">
         <v>0</v>
       </c>
       <c r="P52">
-        <v>0.7074130500000001</v>
+        <v>0.7048213110000001</v>
       </c>
       <c r="Q52">
-        <v>0.9304130500000001</v>
+        <v>0.9278213110000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1549836585022423</v>
+        <v>0.1572118964308595</v>
       </c>
       <c r="T52">
-        <v>1.689036472465245</v>
+        <v>1.723506604556372</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.458983717110404</v>
+        <v>6.332336977559221</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1047268292511211</v>
+        <v>0.1048118292511212</v>
       </c>
       <c r="C53">
-        <v>2.268330490245555</v>
+        <v>2.218605389034463</v>
       </c>
       <c r="D53">
-        <v>4.640560490245554</v>
+        <v>4.638565389034463</v>
       </c>
       <c r="E53">
-        <v>2.24123</v>
+        <v>2.28896</v>
       </c>
       <c r="F53">
-        <v>2.43423</v>
+        <v>2.48196</v>
       </c>
       <c r="G53">
         <v>0.062</v>
@@ -5627,28 +5627,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M53">
-        <v>0.132178689</v>
+        <v>0.134770428</v>
       </c>
       <c r="N53">
-        <v>0.7048213110000001</v>
+        <v>0.702229572</v>
       </c>
       <c r="O53">
         <v>0</v>
       </c>
       <c r="P53">
-        <v>0.7048213110000001</v>
+        <v>0.702229572</v>
       </c>
       <c r="Q53">
-        <v>0.9278213110000001</v>
+        <v>0.925229572</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1572118964308595</v>
+        <v>0.1595329776065024</v>
       </c>
       <c r="T53">
-        <v>1.723506604556372</v>
+        <v>1.759412992151297</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.332336977559221</v>
+        <v>6.210561266452311</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1048118292511212</v>
+        <v>0.1054268292511212</v>
       </c>
       <c r="C54">
-        <v>2.218605389034463</v>
+        <v>2.156491195177485</v>
       </c>
       <c r="D54">
-        <v>4.638565389034463</v>
+        <v>4.624181195177485</v>
       </c>
       <c r="E54">
-        <v>2.28896</v>
+        <v>2.33669</v>
       </c>
       <c r="F54">
-        <v>2.48196</v>
+        <v>2.52969</v>
       </c>
       <c r="G54">
         <v>0.062</v>
@@ -5709,45 +5709,45 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M54">
-        <v>0.134770428</v>
+        <v>0.139891857</v>
       </c>
       <c r="N54">
-        <v>0.702229572</v>
+        <v>0.6971081430000001</v>
       </c>
       <c r="O54">
         <v>0</v>
       </c>
       <c r="P54">
-        <v>0.702229572</v>
+        <v>0.6971081430000001</v>
       </c>
       <c r="Q54">
-        <v>0.925229572</v>
+        <v>0.9201081430000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1595329776065024</v>
+        <v>0.1619528281938748</v>
       </c>
       <c r="T54">
-        <v>1.759412992151297</v>
+        <v>1.796847311133239</v>
       </c>
       <c r="U54">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V54">
         <v>0</v>
       </c>
       <c r="W54">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y54">
-        <v>6.210561266452311</v>
+        <v>5.983193146117148</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1054268292511212</v>
+        <v>0.1055218292511211</v>
       </c>
       <c r="C55">
-        <v>2.156491195177485</v>
+        <v>2.106547197338053</v>
       </c>
       <c r="D55">
-        <v>4.624181195177485</v>
+        <v>4.621967197338052</v>
       </c>
       <c r="E55">
-        <v>2.33669</v>
+        <v>2.38442</v>
       </c>
       <c r="F55">
-        <v>2.52969</v>
+        <v>2.57742</v>
       </c>
       <c r="G55">
         <v>0.062</v>
@@ -5791,28 +5791,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M55">
-        <v>0.139891857</v>
+        <v>0.142531326</v>
       </c>
       <c r="N55">
-        <v>0.6971081430000001</v>
+        <v>0.6944686740000001</v>
       </c>
       <c r="O55">
         <v>0</v>
       </c>
       <c r="P55">
-        <v>0.6971081430000001</v>
+        <v>0.6944686740000001</v>
       </c>
       <c r="Q55">
-        <v>0.9201081430000001</v>
+        <v>0.9174686740000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1619528281938748</v>
+        <v>0.1644778896763503</v>
       </c>
       <c r="T55">
-        <v>1.796847311133239</v>
+        <v>1.835909209201353</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.983193146117148</v>
+        <v>5.872393273040903</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1055218292511211</v>
+        <v>0.1056168292511211</v>
       </c>
       <c r="C56">
-        <v>2.106547197338053</v>
+        <v>2.05660531855081</v>
       </c>
       <c r="D56">
-        <v>4.621967197338052</v>
+        <v>4.61975531855081</v>
       </c>
       <c r="E56">
-        <v>2.38442</v>
+        <v>2.43215</v>
       </c>
       <c r="F56">
-        <v>2.57742</v>
+        <v>2.62515</v>
       </c>
       <c r="G56">
         <v>0.062</v>
@@ -5873,28 +5873,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M56">
-        <v>0.142531326</v>
+        <v>0.145170795</v>
       </c>
       <c r="N56">
-        <v>0.6944686740000001</v>
+        <v>0.6918292050000001</v>
       </c>
       <c r="O56">
         <v>0</v>
       </c>
       <c r="P56">
-        <v>0.6944686740000001</v>
+        <v>0.6918292050000001</v>
       </c>
       <c r="Q56">
-        <v>0.9174686740000001</v>
+        <v>0.9148292050000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1644778896763503</v>
+        <v>0.1671151761136026</v>
       </c>
       <c r="T56">
-        <v>1.835909209201353</v>
+        <v>1.87670719162805</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.872393273040903</v>
+        <v>5.765622486258342</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1056168292511211</v>
+        <v>0.1057118292511212</v>
       </c>
       <c r="C57">
-        <v>2.05660531855081</v>
+        <v>2.006665555774945</v>
       </c>
       <c r="D57">
-        <v>4.61975531855081</v>
+        <v>4.617545555774945</v>
       </c>
       <c r="E57">
-        <v>2.43215</v>
+        <v>2.47988</v>
       </c>
       <c r="F57">
-        <v>2.62515</v>
+        <v>2.67288</v>
       </c>
       <c r="G57">
         <v>0.062</v>
@@ -5955,28 +5955,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M57">
-        <v>0.145170795</v>
+        <v>0.147810264</v>
       </c>
       <c r="N57">
-        <v>0.6918292050000001</v>
+        <v>0.6891897360000001</v>
       </c>
       <c r="O57">
         <v>0</v>
       </c>
       <c r="P57">
-        <v>0.6918292050000001</v>
+        <v>0.6891897360000001</v>
       </c>
       <c r="Q57">
-        <v>0.9148292050000001</v>
+        <v>0.9121897360000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1671151761136026</v>
+        <v>0.1698723392070935</v>
       </c>
       <c r="T57">
-        <v>1.87670719162805</v>
+        <v>1.919359627801415</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.765622486258342</v>
+        <v>5.662664941860871</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1057118292511212</v>
+        <v>0.1058068292511212</v>
       </c>
       <c r="C58">
-        <v>2.006665555774945</v>
+        <v>1.95672790597546</v>
       </c>
       <c r="D58">
-        <v>4.617545555774945</v>
+        <v>4.61533790597546</v>
       </c>
       <c r="E58">
-        <v>2.47988</v>
+        <v>2.52761</v>
       </c>
       <c r="F58">
-        <v>2.67288</v>
+        <v>2.72061</v>
       </c>
       <c r="G58">
         <v>0.062</v>
@@ -6037,28 +6037,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M58">
-        <v>0.147810264</v>
+        <v>0.150449733</v>
       </c>
       <c r="N58">
-        <v>0.6891897360000001</v>
+        <v>0.6865502670000001</v>
       </c>
       <c r="O58">
         <v>0</v>
       </c>
       <c r="P58">
-        <v>0.6891897360000001</v>
+        <v>0.6865502670000001</v>
       </c>
       <c r="Q58">
-        <v>0.9121897360000001</v>
+        <v>0.9095502670000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1698723392070935</v>
+        <v>0.1727577424444678</v>
       </c>
       <c r="T58">
-        <v>1.919359627801415</v>
+        <v>1.963995898215401</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.662664941860871</v>
+        <v>5.563319942880856</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1058068292511212</v>
+        <v>0.1059018292511212</v>
       </c>
       <c r="C59">
-        <v>1.95672790597546</v>
+        <v>1.906792366123163</v>
       </c>
       <c r="D59">
-        <v>4.61533790597546</v>
+        <v>4.613132366123163</v>
       </c>
       <c r="E59">
-        <v>2.52761</v>
+        <v>2.57534</v>
       </c>
       <c r="F59">
-        <v>2.72061</v>
+        <v>2.76834</v>
       </c>
       <c r="G59">
         <v>0.062</v>
@@ -6119,28 +6119,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M59">
-        <v>0.150449733</v>
+        <v>0.153089202</v>
       </c>
       <c r="N59">
-        <v>0.6865502670000001</v>
+        <v>0.6839107980000001</v>
       </c>
       <c r="O59">
         <v>0</v>
       </c>
       <c r="P59">
-        <v>0.6865502670000001</v>
+        <v>0.6839107980000001</v>
       </c>
       <c r="Q59">
-        <v>0.9095502670000001</v>
+        <v>0.9069107980000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1727577424444678</v>
+        <v>0.1757805458360028</v>
       </c>
       <c r="T59">
-        <v>1.963995898215401</v>
+        <v>2.010757705315768</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.563319942880856</v>
+        <v>5.467400633520842</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1059018292511212</v>
+        <v>0.1059968292511212</v>
       </c>
       <c r="C60">
-        <v>1.906792366123164</v>
+        <v>1.856858933194643</v>
       </c>
       <c r="D60">
-        <v>4.613132366123163</v>
+        <v>4.610928933194643</v>
       </c>
       <c r="E60">
-        <v>2.57534</v>
+        <v>2.62307</v>
       </c>
       <c r="F60">
-        <v>2.76834</v>
+        <v>2.81607</v>
       </c>
       <c r="G60">
         <v>0.062</v>
@@ -6201,28 +6201,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M60">
-        <v>0.153089202</v>
+        <v>0.155728671</v>
       </c>
       <c r="N60">
-        <v>0.6839107980000001</v>
+        <v>0.6812713290000001</v>
       </c>
       <c r="O60">
         <v>0</v>
       </c>
       <c r="P60">
-        <v>0.6839107980000001</v>
+        <v>0.6812713290000001</v>
       </c>
       <c r="Q60">
-        <v>0.9069107980000001</v>
+        <v>0.9042713290000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1757805458360027</v>
+        <v>0.178950803051515</v>
       </c>
       <c r="T60">
-        <v>2.010757705315767</v>
+        <v>2.059800576177127</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.467400633520842</v>
+        <v>5.374732826173031</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1059968292511212</v>
+        <v>0.1060918292511212</v>
       </c>
       <c r="C61">
-        <v>1.856858933194643</v>
+        <v>1.806927604172266</v>
       </c>
       <c r="D61">
-        <v>4.610928933194643</v>
+        <v>4.608727604172266</v>
       </c>
       <c r="E61">
-        <v>2.62307</v>
+        <v>2.6708</v>
       </c>
       <c r="F61">
-        <v>2.81607</v>
+        <v>2.8638</v>
       </c>
       <c r="G61">
         <v>0.062</v>
@@ -6283,28 +6283,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M61">
-        <v>0.155728671</v>
+        <v>0.15836814</v>
       </c>
       <c r="N61">
-        <v>0.6812713290000001</v>
+        <v>0.6786318600000001</v>
       </c>
       <c r="O61">
         <v>0</v>
       </c>
       <c r="P61">
-        <v>0.6812713290000001</v>
+        <v>0.6786318600000001</v>
       </c>
       <c r="Q61">
-        <v>0.9042713290000001</v>
+        <v>0.9016318600000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.178950803051515</v>
+        <v>0.1822795731278029</v>
       </c>
       <c r="T61">
-        <v>2.059800576177127</v>
+        <v>2.111295590581556</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.374732826173031</v>
+        <v>5.285153945736814</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1060918292511212</v>
+        <v>0.1061868292511211</v>
       </c>
       <c r="C62">
-        <v>1.806927604172266</v>
+        <v>1.756998376044158</v>
       </c>
       <c r="D62">
-        <v>4.608727604172266</v>
+        <v>4.606528376044158</v>
       </c>
       <c r="E62">
-        <v>2.6708</v>
+        <v>2.71853</v>
       </c>
       <c r="F62">
-        <v>2.8638</v>
+        <v>2.91153</v>
       </c>
       <c r="G62">
         <v>0.062</v>
@@ -6365,28 +6365,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M62">
-        <v>0.15836814</v>
+        <v>0.161007609</v>
       </c>
       <c r="N62">
-        <v>0.6786318600000001</v>
+        <v>0.6759923910000001</v>
       </c>
       <c r="O62">
         <v>0</v>
       </c>
       <c r="P62">
-        <v>0.6786318600000001</v>
+        <v>0.6759923910000001</v>
       </c>
       <c r="Q62">
-        <v>0.9016318600000001</v>
+        <v>0.8989923910000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1822795731278029</v>
+        <v>0.1857790493618491</v>
       </c>
       <c r="T62">
-        <v>2.111295590581556</v>
+        <v>2.165431374955442</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.285153945736814</v>
+        <v>5.198512077773915</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1061868292511211</v>
+        <v>0.1062818292511212</v>
       </c>
       <c r="C63">
-        <v>1.756998376044158</v>
+        <v>1.70707124580419</v>
       </c>
       <c r="D63">
-        <v>4.606528376044158</v>
+        <v>4.60433124580419</v>
       </c>
       <c r="E63">
-        <v>2.71853</v>
+        <v>2.76626</v>
       </c>
       <c r="F63">
-        <v>2.91153</v>
+        <v>2.95926</v>
       </c>
       <c r="G63">
         <v>0.062</v>
@@ -6447,28 +6447,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M63">
-        <v>0.161007609</v>
+        <v>0.163647078</v>
       </c>
       <c r="N63">
-        <v>0.6759923910000001</v>
+        <v>0.6733529220000001</v>
       </c>
       <c r="O63">
         <v>0</v>
       </c>
       <c r="P63">
-        <v>0.6759923910000001</v>
+        <v>0.6733529220000001</v>
       </c>
       <c r="Q63">
-        <v>0.8989923910000001</v>
+        <v>0.8963529220000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1857790493618491</v>
+        <v>0.189462708555582</v>
       </c>
       <c r="T63">
-        <v>2.165431374955442</v>
+        <v>2.22241641113848</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.198512077773915</v>
+        <v>5.114665108777562</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1062818292511212</v>
+        <v>0.1063768292511212</v>
       </c>
       <c r="C64">
-        <v>1.70707124580419</v>
+        <v>1.657146210451967</v>
       </c>
       <c r="D64">
-        <v>4.60433124580419</v>
+        <v>4.602136210451967</v>
       </c>
       <c r="E64">
-        <v>2.76626</v>
+        <v>2.81399</v>
       </c>
       <c r="F64">
-        <v>2.95926</v>
+        <v>3.00699</v>
       </c>
       <c r="G64">
         <v>0.062</v>
@@ -6529,28 +6529,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M64">
-        <v>0.163647078</v>
+        <v>0.166286547</v>
       </c>
       <c r="N64">
-        <v>0.6733529220000001</v>
+        <v>0.6707134530000001</v>
       </c>
       <c r="O64">
         <v>0</v>
       </c>
       <c r="P64">
-        <v>0.6733529220000001</v>
+        <v>0.6707134530000001</v>
       </c>
       <c r="Q64">
-        <v>0.8963529220000001</v>
+        <v>0.893713453</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.189462708555582</v>
+        <v>0.1933454844624896</v>
       </c>
       <c r="T64">
-        <v>2.22241641113848</v>
+        <v>2.282481719547628</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.114665108777562</v>
+        <v>5.033479948320775</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1063768292511212</v>
+        <v>0.1064718292511211</v>
       </c>
       <c r="C65">
-        <v>1.657146210451967</v>
+        <v>1.607223266992813</v>
       </c>
       <c r="D65">
-        <v>4.602136210451967</v>
+        <v>4.599943266992812</v>
       </c>
       <c r="E65">
-        <v>2.81399</v>
+        <v>2.86172</v>
       </c>
       <c r="F65">
-        <v>3.00699</v>
+        <v>3.05472</v>
       </c>
       <c r="G65">
         <v>0.062</v>
@@ -6611,28 +6611,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M65">
-        <v>0.166286547</v>
+        <v>0.168926016</v>
       </c>
       <c r="N65">
-        <v>0.6707134530000001</v>
+        <v>0.6680739840000001</v>
       </c>
       <c r="O65">
         <v>0</v>
       </c>
       <c r="P65">
-        <v>0.6707134530000001</v>
+        <v>0.6680739840000001</v>
       </c>
       <c r="Q65">
-        <v>0.893713453</v>
+        <v>0.891073984</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1933454844624896</v>
+        <v>0.1974439701420032</v>
       </c>
       <c r="T65">
-        <v>2.282481719547628</v>
+        <v>2.345883989535062</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.033479948320775</v>
+        <v>4.954831824128263</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1064718292511211</v>
+        <v>0.1065668292511212</v>
       </c>
       <c r="C66">
-        <v>1.607223266992813</v>
+        <v>1.557302412437755</v>
       </c>
       <c r="D66">
-        <v>4.599943266992812</v>
+        <v>4.597752412437754</v>
       </c>
       <c r="E66">
-        <v>2.86172</v>
+        <v>2.90945</v>
       </c>
       <c r="F66">
-        <v>3.05472</v>
+        <v>3.10245</v>
       </c>
       <c r="G66">
         <v>0.062</v>
@@ -6693,28 +6693,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M66">
-        <v>0.168926016</v>
+        <v>0.171565485</v>
       </c>
       <c r="N66">
-        <v>0.6680739840000001</v>
+        <v>0.6654345150000001</v>
       </c>
       <c r="O66">
         <v>0</v>
       </c>
       <c r="P66">
-        <v>0.6680739840000001</v>
+        <v>0.6654345150000001</v>
       </c>
       <c r="Q66">
-        <v>0.891073984</v>
+        <v>0.888434515</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1974439701420032</v>
+        <v>0.2017766550032033</v>
       </c>
       <c r="T66">
-        <v>2.345883989535062</v>
+        <v>2.412909246378921</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.954831824128263</v>
+        <v>4.878603642218597</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1065668292511212</v>
+        <v>0.1066618292511212</v>
       </c>
       <c r="C67">
-        <v>1.557302412437755</v>
+        <v>1.507383643803512</v>
       </c>
       <c r="D67">
-        <v>4.597752412437754</v>
+        <v>4.595563643803511</v>
       </c>
       <c r="E67">
-        <v>2.90945</v>
+        <v>2.95718</v>
       </c>
       <c r="F67">
-        <v>3.10245</v>
+        <v>3.15018</v>
       </c>
       <c r="G67">
         <v>0.062</v>
@@ -6775,28 +6775,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M67">
-        <v>0.171565485</v>
+        <v>0.174204954</v>
       </c>
       <c r="N67">
-        <v>0.6654345150000001</v>
+        <v>0.6627950460000001</v>
       </c>
       <c r="O67">
         <v>0</v>
       </c>
       <c r="P67">
-        <v>0.6654345150000001</v>
+        <v>0.6627950460000001</v>
       </c>
       <c r="Q67">
-        <v>0.888434515</v>
+        <v>0.885795046</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2017766550032033</v>
+        <v>0.2063642036797681</v>
       </c>
       <c r="T67">
-        <v>2.412909246378921</v>
+        <v>2.483877165390066</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.878603642218597</v>
+        <v>4.804685405215285</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1066618292511212</v>
+        <v>0.1067568292511211</v>
       </c>
       <c r="C68">
-        <v>1.507383643803512</v>
+        <v>1.457466958112484</v>
       </c>
       <c r="D68">
-        <v>4.595563643803511</v>
+        <v>4.593376958112484</v>
       </c>
       <c r="E68">
-        <v>2.95718</v>
+        <v>3.00491</v>
       </c>
       <c r="F68">
-        <v>3.15018</v>
+        <v>3.19791</v>
       </c>
       <c r="G68">
         <v>0.062</v>
@@ -6857,28 +6857,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M68">
-        <v>0.174204954</v>
+        <v>0.176844423</v>
       </c>
       <c r="N68">
-        <v>0.6627950460000001</v>
+        <v>0.660155577</v>
       </c>
       <c r="O68">
         <v>0</v>
       </c>
       <c r="P68">
-        <v>0.6627950460000001</v>
+        <v>0.660155577</v>
       </c>
       <c r="Q68">
-        <v>0.885795046</v>
+        <v>0.883155577</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2063642036797681</v>
+        <v>0.2112297856094581</v>
       </c>
       <c r="T68">
-        <v>2.483877165390066</v>
+        <v>2.559146170401886</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.804685405215285</v>
+        <v>4.732973682749385</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1067568292511211</v>
+        <v>0.1068518292511212</v>
       </c>
       <c r="C69">
-        <v>1.457466958112484</v>
+        <v>1.407552352392733</v>
       </c>
       <c r="D69">
-        <v>4.593376958112484</v>
+        <v>4.591192352392732</v>
       </c>
       <c r="E69">
-        <v>3.00491</v>
+        <v>3.05264</v>
       </c>
       <c r="F69">
-        <v>3.19791</v>
+        <v>3.24564</v>
       </c>
       <c r="G69">
         <v>0.062</v>
@@ -6939,28 +6939,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M69">
-        <v>0.176844423</v>
+        <v>0.179483892</v>
       </c>
       <c r="N69">
-        <v>0.660155577</v>
+        <v>0.657516108</v>
       </c>
       <c r="O69">
         <v>0</v>
       </c>
       <c r="P69">
-        <v>0.660155577</v>
+        <v>0.657516108</v>
       </c>
       <c r="Q69">
-        <v>0.883155577</v>
+        <v>0.880516108</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2112297856094581</v>
+        <v>0.2163994664097536</v>
       </c>
       <c r="T69">
-        <v>2.559146170401886</v>
+        <v>2.639119488226945</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.732973682749385</v>
+        <v>4.663371128591306</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1068518292511212</v>
+        <v>0.1069468292511212</v>
       </c>
       <c r="C70">
-        <v>1.407552352392733</v>
+        <v>1.357639823677971</v>
       </c>
       <c r="D70">
-        <v>4.591192352392732</v>
+        <v>4.58900982367797</v>
       </c>
       <c r="E70">
-        <v>3.05264</v>
+        <v>3.10037</v>
       </c>
       <c r="F70">
-        <v>3.24564</v>
+        <v>3.29337</v>
       </c>
       <c r="G70">
         <v>0.062</v>
@@ -7021,28 +7021,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M70">
-        <v>0.179483892</v>
+        <v>0.182123361</v>
       </c>
       <c r="N70">
-        <v>0.657516108</v>
+        <v>0.654876639</v>
       </c>
       <c r="O70">
         <v>0</v>
       </c>
       <c r="P70">
-        <v>0.657516108</v>
+        <v>0.654876639</v>
       </c>
       <c r="Q70">
-        <v>0.880516108</v>
+        <v>0.877876639</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2163994664097536</v>
+        <v>0.2219026750036167</v>
       </c>
       <c r="T70">
-        <v>2.639119488226945</v>
+        <v>2.724252374943944</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.663371128591306</v>
+        <v>4.595786039771141</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1069468292511212</v>
+        <v>0.1070418292511212</v>
       </c>
       <c r="C71">
-        <v>1.357639823677971</v>
+        <v>1.307729369007551</v>
       </c>
       <c r="D71">
-        <v>4.58900982367797</v>
+        <v>4.586829369007551</v>
       </c>
       <c r="E71">
-        <v>3.10037</v>
+        <v>3.1481</v>
       </c>
       <c r="F71">
-        <v>3.29337</v>
+        <v>3.3411</v>
       </c>
       <c r="G71">
         <v>0.062</v>
@@ -7103,28 +7103,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M71">
-        <v>0.182123361</v>
+        <v>0.18476283</v>
       </c>
       <c r="N71">
-        <v>0.654876639</v>
+        <v>0.65223717</v>
       </c>
       <c r="O71">
         <v>0</v>
       </c>
       <c r="P71">
-        <v>0.654876639</v>
+        <v>0.65223717</v>
       </c>
       <c r="Q71">
-        <v>0.877876639</v>
+        <v>0.87523717</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2219026750036167</v>
+        <v>0.2277727641704039</v>
       </c>
       <c r="T71">
-        <v>2.724252374943944</v>
+        <v>2.815060787442075</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.595786039771141</v>
+        <v>4.530131953488697</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1070418292511212</v>
+        <v>0.1089118292511212</v>
       </c>
       <c r="C72">
-        <v>1.307729369007551</v>
+        <v>1.217496756286467</v>
       </c>
       <c r="D72">
-        <v>4.586829369007551</v>
+        <v>4.544326756286467</v>
       </c>
       <c r="E72">
-        <v>3.1481</v>
+        <v>3.19583</v>
       </c>
       <c r="F72">
-        <v>3.3411</v>
+        <v>3.38883</v>
       </c>
       <c r="G72">
         <v>0.062</v>
@@ -7185,45 +7185,45 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M72">
-        <v>0.18476283</v>
+        <v>0.195874374</v>
       </c>
       <c r="N72">
-        <v>0.65223717</v>
+        <v>0.641125626</v>
       </c>
       <c r="O72">
         <v>0</v>
       </c>
       <c r="P72">
-        <v>0.65223717</v>
+        <v>0.641125626</v>
       </c>
       <c r="Q72">
-        <v>0.87523717</v>
+        <v>0.864125626</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2277727641704039</v>
+        <v>0.2340476870728316</v>
       </c>
       <c r="T72">
-        <v>2.815060787442075</v>
+        <v>2.912131849078009</v>
       </c>
       <c r="U72">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V72">
         <v>0</v>
       </c>
       <c r="W72">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y72">
-        <v>4.530131953488697</v>
+        <v>4.27314703249543</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1089118292511212</v>
+        <v>0.1090318292511212</v>
       </c>
       <c r="C73">
-        <v>1.217496756286468</v>
+        <v>1.167066194805597</v>
       </c>
       <c r="D73">
-        <v>4.544326756286467</v>
+        <v>4.541626194805596</v>
       </c>
       <c r="E73">
-        <v>3.19583</v>
+        <v>3.24356</v>
       </c>
       <c r="F73">
-        <v>3.38883</v>
+        <v>3.43656</v>
       </c>
       <c r="G73">
         <v>0.062</v>
@@ -7267,28 +7267,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M73">
-        <v>0.195874374</v>
+        <v>0.198633168</v>
       </c>
       <c r="N73">
-        <v>0.6411256260000001</v>
+        <v>0.6383668320000001</v>
       </c>
       <c r="O73">
         <v>0</v>
       </c>
       <c r="P73">
-        <v>0.6411256260000001</v>
+        <v>0.6383668320000001</v>
       </c>
       <c r="Q73">
-        <v>0.8641256260000001</v>
+        <v>0.8613668320000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2340476870728316</v>
+        <v>0.2407708187540041</v>
       </c>
       <c r="T73">
-        <v>2.912131849078008</v>
+        <v>3.016136557973651</v>
       </c>
       <c r="U73">
         <v>0.0578</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.27314703249543</v>
+        <v>4.213797768155216</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1090318292511212</v>
+        <v>0.1091518292511212</v>
       </c>
       <c r="C74">
-        <v>1.167066194805597</v>
+        <v>1.116638841149006</v>
       </c>
       <c r="D74">
-        <v>4.541626194805596</v>
+        <v>4.538928841149005</v>
       </c>
       <c r="E74">
-        <v>3.24356</v>
+        <v>3.29129</v>
       </c>
       <c r="F74">
-        <v>3.43656</v>
+        <v>3.48429</v>
       </c>
       <c r="G74">
         <v>0.062</v>
@@ -7349,28 +7349,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M74">
-        <v>0.198633168</v>
+        <v>0.201391962</v>
       </c>
       <c r="N74">
-        <v>0.6383668320000001</v>
+        <v>0.6356080380000001</v>
       </c>
       <c r="O74">
         <v>0</v>
       </c>
       <c r="P74">
-        <v>0.6383668320000001</v>
+        <v>0.6356080380000001</v>
       </c>
       <c r="Q74">
-        <v>0.8613668320000001</v>
+        <v>0.8586080380000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2407708187540041</v>
+        <v>0.2479919601893376</v>
       </c>
       <c r="T74">
-        <v>3.016136557973651</v>
+        <v>3.127845319380083</v>
       </c>
       <c r="U74">
         <v>0.0578</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.213797768155216</v>
+        <v>4.156074511057199</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1091518292511212</v>
+        <v>0.1092718292511212</v>
       </c>
       <c r="C75">
-        <v>1.116638841149006</v>
+        <v>1.06621468960453</v>
       </c>
       <c r="D75">
-        <v>4.538928841149005</v>
+        <v>4.536234689604529</v>
       </c>
       <c r="E75">
-        <v>3.29129</v>
+        <v>3.33902</v>
       </c>
       <c r="F75">
-        <v>3.48429</v>
+        <v>3.53202</v>
       </c>
       <c r="G75">
         <v>0.062</v>
@@ -7431,28 +7431,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M75">
-        <v>0.201391962</v>
+        <v>0.204150756</v>
       </c>
       <c r="N75">
-        <v>0.6356080380000001</v>
+        <v>0.6328492440000001</v>
       </c>
       <c r="O75">
         <v>0</v>
       </c>
       <c r="P75">
-        <v>0.6356080380000001</v>
+        <v>0.6328492440000001</v>
       </c>
       <c r="Q75">
-        <v>0.8586080380000001</v>
+        <v>0.8558492440000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2479919601893376</v>
+        <v>0.2557685740427736</v>
       </c>
       <c r="T75">
-        <v>3.127845319380083</v>
+        <v>3.248147062433163</v>
       </c>
       <c r="U75">
         <v>0.0578</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.156074511057199</v>
+        <v>4.099911341988859</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1092718292511212</v>
+        <v>0.1093918292511211</v>
       </c>
       <c r="C76">
-        <v>1.06621468960453</v>
+        <v>1.015793734473564</v>
       </c>
       <c r="D76">
-        <v>4.536234689604529</v>
+        <v>4.533543734473564</v>
       </c>
       <c r="E76">
-        <v>3.33902</v>
+        <v>3.38675</v>
       </c>
       <c r="F76">
-        <v>3.53202</v>
+        <v>3.57975</v>
       </c>
       <c r="G76">
         <v>0.062</v>
@@ -7513,28 +7513,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M76">
-        <v>0.204150756</v>
+        <v>0.20690955</v>
       </c>
       <c r="N76">
-        <v>0.6328492440000001</v>
+        <v>0.6300904500000001</v>
       </c>
       <c r="O76">
         <v>0</v>
       </c>
       <c r="P76">
-        <v>0.6328492440000001</v>
+        <v>0.6300904500000001</v>
       </c>
       <c r="Q76">
-        <v>0.8558492440000001</v>
+        <v>0.8530904500000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2557685740427736</v>
+        <v>0.2641673170044846</v>
       </c>
       <c r="T76">
-        <v>3.248147062433163</v>
+        <v>3.378072944930489</v>
       </c>
       <c r="U76">
         <v>0.0578</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.099911341988859</v>
+        <v>4.045245857429007</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1093918292511211</v>
+        <v>0.1121718292511212</v>
       </c>
       <c r="C77">
-        <v>1.015793734473564</v>
+        <v>0.9066048705796494</v>
       </c>
       <c r="D77">
-        <v>4.533543734473564</v>
+        <v>4.472084870579649</v>
       </c>
       <c r="E77">
-        <v>3.38675</v>
+        <v>3.43448</v>
       </c>
       <c r="F77">
-        <v>3.57975</v>
+        <v>3.62748</v>
       </c>
       <c r="G77">
         <v>0.062</v>
@@ -7595,45 +7595,45 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M77">
-        <v>0.20690955</v>
+        <v>0.222364524</v>
       </c>
       <c r="N77">
-        <v>0.6300904500000001</v>
+        <v>0.6146354760000001</v>
       </c>
       <c r="O77">
         <v>0</v>
       </c>
       <c r="P77">
-        <v>0.6300904500000001</v>
+        <v>0.6146354760000001</v>
       </c>
       <c r="Q77">
-        <v>0.8530904500000001</v>
+        <v>0.8376354760000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2641673170044846</v>
+        <v>0.2732659552130048</v>
       </c>
       <c r="T77">
-        <v>3.378072944930489</v>
+        <v>3.518825984302593</v>
       </c>
       <c r="U77">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V77">
         <v>0</v>
       </c>
       <c r="W77">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y77">
-        <v>4.045245857429007</v>
+        <v>3.764089635089454</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1121718292511212</v>
+        <v>0.1123268292511211</v>
       </c>
       <c r="C78">
-        <v>0.9066048705796494</v>
+        <v>0.8554972137638179</v>
       </c>
       <c r="D78">
-        <v>4.472084870579649</v>
+        <v>4.468707213763818</v>
       </c>
       <c r="E78">
-        <v>3.43448</v>
+        <v>3.48221</v>
       </c>
       <c r="F78">
-        <v>3.62748</v>
+        <v>3.67521</v>
       </c>
       <c r="G78">
         <v>0.062</v>
@@ -7677,28 +7677,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M78">
-        <v>0.222364524</v>
+        <v>0.225290373</v>
       </c>
       <c r="N78">
-        <v>0.6146354760000001</v>
+        <v>0.6117096270000001</v>
       </c>
       <c r="O78">
         <v>0</v>
       </c>
       <c r="P78">
-        <v>0.6146354760000001</v>
+        <v>0.6117096270000001</v>
       </c>
       <c r="Q78">
-        <v>0.8376354760000001</v>
+        <v>0.8347096270000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2732659552130048</v>
+        <v>0.2831557793527006</v>
       </c>
       <c r="T78">
-        <v>3.518825984302593</v>
+        <v>3.671818418402706</v>
       </c>
       <c r="U78">
         <v>0.0613</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.764089635089454</v>
+        <v>3.715205354114266</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1123268292511211</v>
+        <v>0.1124818292511212</v>
       </c>
       <c r="C79">
-        <v>0.8554972137638179</v>
+        <v>0.8043946552212904</v>
       </c>
       <c r="D79">
-        <v>4.468707213763818</v>
+        <v>4.46533465522129</v>
       </c>
       <c r="E79">
-        <v>3.48221</v>
+        <v>3.52994</v>
       </c>
       <c r="F79">
-        <v>3.67521</v>
+        <v>3.72294</v>
       </c>
       <c r="G79">
         <v>0.062</v>
@@ -7759,28 +7759,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M79">
-        <v>0.225290373</v>
+        <v>0.228216222</v>
       </c>
       <c r="N79">
-        <v>0.6117096270000001</v>
+        <v>0.6087837780000001</v>
       </c>
       <c r="O79">
         <v>0</v>
       </c>
       <c r="P79">
-        <v>0.6117096270000001</v>
+        <v>0.6087837780000001</v>
       </c>
       <c r="Q79">
-        <v>0.8347096270000001</v>
+        <v>0.831783778</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2831557793527006</v>
+        <v>0.2939446784141871</v>
       </c>
       <c r="T79">
-        <v>3.671818418402706</v>
+        <v>3.838719255602829</v>
       </c>
       <c r="U79">
         <v>0.0613</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.715205354114266</v>
+        <v>3.667574516241006</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1124818292511212</v>
+        <v>0.1126368292511211</v>
       </c>
       <c r="C80">
-        <v>0.8043946552212904</v>
+        <v>0.753297183417688</v>
       </c>
       <c r="D80">
-        <v>4.46533465522129</v>
+        <v>4.461967183417688</v>
       </c>
       <c r="E80">
-        <v>3.52994</v>
+        <v>3.57767</v>
       </c>
       <c r="F80">
-        <v>3.72294</v>
+        <v>3.77067</v>
       </c>
       <c r="G80">
         <v>0.062</v>
@@ -7841,28 +7841,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M80">
-        <v>0.228216222</v>
+        <v>0.231142071</v>
       </c>
       <c r="N80">
-        <v>0.6087837780000001</v>
+        <v>0.6058579290000001</v>
       </c>
       <c r="O80">
         <v>0</v>
       </c>
       <c r="P80">
-        <v>0.6087837780000001</v>
+        <v>0.6058579290000001</v>
       </c>
       <c r="Q80">
-        <v>0.831783778</v>
+        <v>0.8288579290000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2939446784141871</v>
+        <v>0.3057610916720055</v>
       </c>
       <c r="T80">
-        <v>3.838719255602829</v>
+        <v>4.021515410631536</v>
       </c>
       <c r="U80">
         <v>0.0613</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.667574516241006</v>
+        <v>3.621149522364538</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1126368292511211</v>
+        <v>0.1127918292511211</v>
       </c>
       <c r="C81">
-        <v>0.753297183417688</v>
+        <v>0.7022047868533936</v>
       </c>
       <c r="D81">
-        <v>4.461967183417688</v>
+        <v>4.458604786853393</v>
       </c>
       <c r="E81">
-        <v>3.57767</v>
+        <v>3.6254</v>
       </c>
       <c r="F81">
-        <v>3.77067</v>
+        <v>3.8184</v>
       </c>
       <c r="G81">
         <v>0.062</v>
@@ -7923,28 +7923,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M81">
-        <v>0.231142071</v>
+        <v>0.23406792</v>
       </c>
       <c r="N81">
-        <v>0.6058579290000001</v>
+        <v>0.6029320800000001</v>
       </c>
       <c r="O81">
         <v>0</v>
       </c>
       <c r="P81">
-        <v>0.6058579290000001</v>
+        <v>0.6029320800000001</v>
       </c>
       <c r="Q81">
-        <v>0.8288579290000001</v>
+        <v>0.8259320800000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3057610916720055</v>
+        <v>0.3187591462556058</v>
       </c>
       <c r="T81">
-        <v>4.021515410631536</v>
+        <v>4.222591181163112</v>
       </c>
       <c r="U81">
         <v>0.0613</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.621149522364538</v>
+        <v>3.575885153334981</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1127918292511211</v>
+        <v>0.1129468292511212</v>
       </c>
       <c r="C82">
-        <v>0.7022047868533936</v>
+        <v>0.6511174540634306</v>
       </c>
       <c r="D82">
-        <v>4.458604786853393</v>
+        <v>4.45524745406343</v>
       </c>
       <c r="E82">
-        <v>3.6254</v>
+        <v>3.67313</v>
       </c>
       <c r="F82">
-        <v>3.8184</v>
+        <v>3.86613</v>
       </c>
       <c r="G82">
         <v>0.062</v>
@@ -8005,28 +8005,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M82">
-        <v>0.23406792</v>
+        <v>0.236993769</v>
       </c>
       <c r="N82">
-        <v>0.6029320800000001</v>
+        <v>0.6000062310000001</v>
       </c>
       <c r="O82">
         <v>0</v>
       </c>
       <c r="P82">
-        <v>0.6029320800000001</v>
+        <v>0.6000062310000001</v>
       </c>
       <c r="Q82">
-        <v>0.8259320800000001</v>
+        <v>0.823006231</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3187591462556058</v>
+        <v>0.3331254171111641</v>
       </c>
       <c r="T82">
-        <v>4.222591181163112</v>
+        <v>4.444832822276961</v>
       </c>
       <c r="U82">
         <v>0.0613</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.575885153334981</v>
+        <v>3.531738423046895</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1129468292511212</v>
+        <v>0.1153978292511212</v>
       </c>
       <c r="C83">
-        <v>0.6511174540634306</v>
+        <v>0.5509624826033535</v>
       </c>
       <c r="D83">
-        <v>4.45524745406343</v>
+        <v>4.402822482603353</v>
       </c>
       <c r="E83">
-        <v>3.67313</v>
+        <v>3.72086</v>
       </c>
       <c r="F83">
-        <v>3.86613</v>
+        <v>3.91386</v>
       </c>
       <c r="G83">
         <v>0.062</v>
@@ -8087,45 +8087,45 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M83">
-        <v>0.236993769</v>
+        <v>0.250878426</v>
       </c>
       <c r="N83">
-        <v>0.6000062310000001</v>
+        <v>0.5861215740000001</v>
       </c>
       <c r="O83">
         <v>0</v>
       </c>
       <c r="P83">
-        <v>0.6000062310000001</v>
+        <v>0.5861215740000001</v>
       </c>
       <c r="Q83">
-        <v>0.823006231</v>
+        <v>0.8091215740000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3331254171111641</v>
+        <v>0.3490879402840065</v>
       </c>
       <c r="T83">
-        <v>4.444832822276961</v>
+        <v>4.691767979070126</v>
       </c>
       <c r="U83">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V83">
         <v>0</v>
       </c>
       <c r="W83">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y83">
-        <v>3.531738423046895</v>
+        <v>3.336277309073997</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1153978292511212</v>
+        <v>0.1155808292511212</v>
       </c>
       <c r="C84">
-        <v>0.5509624826033535</v>
+        <v>0.4993677100757523</v>
       </c>
       <c r="D84">
-        <v>4.402822482603353</v>
+        <v>4.398957710075752</v>
       </c>
       <c r="E84">
-        <v>3.72086</v>
+        <v>3.76859</v>
       </c>
       <c r="F84">
-        <v>3.91386</v>
+        <v>3.96159</v>
       </c>
       <c r="G84">
         <v>0.062</v>
@@ -8169,28 +8169,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M84">
-        <v>0.250878426</v>
+        <v>0.253937919</v>
       </c>
       <c r="N84">
-        <v>0.5861215740000001</v>
+        <v>0.583062081</v>
       </c>
       <c r="O84">
         <v>0</v>
       </c>
       <c r="P84">
-        <v>0.5861215740000001</v>
+        <v>0.583062081</v>
       </c>
       <c r="Q84">
-        <v>0.8091215740000001</v>
+        <v>0.806062081</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3490879402840065</v>
+        <v>0.3669284073595364</v>
       </c>
       <c r="T84">
-        <v>4.691767979070126</v>
+        <v>4.967754330780133</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.336277309073997</v>
+        <v>3.296081196916479</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1155808292511212</v>
+        <v>0.1157638292511212</v>
       </c>
       <c r="C85">
-        <v>0.4993677100757523</v>
+        <v>0.4477797165482595</v>
       </c>
       <c r="D85">
-        <v>4.398957710075752</v>
+        <v>4.395099716548259</v>
       </c>
       <c r="E85">
-        <v>3.76859</v>
+        <v>3.81632</v>
       </c>
       <c r="F85">
-        <v>3.96159</v>
+        <v>4.00932</v>
       </c>
       <c r="G85">
         <v>0.062</v>
@@ -8251,28 +8251,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M85">
-        <v>0.253937919</v>
+        <v>0.256997412</v>
       </c>
       <c r="N85">
-        <v>0.583062081</v>
+        <v>0.5800025880000002</v>
       </c>
       <c r="O85">
         <v>0</v>
       </c>
       <c r="P85">
-        <v>0.583062081</v>
+        <v>0.5800025880000002</v>
       </c>
       <c r="Q85">
-        <v>0.806062081</v>
+        <v>0.8030025880000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3669284073595364</v>
+        <v>0.3869989328195074</v>
       </c>
       <c r="T85">
-        <v>4.967754330780133</v>
+        <v>5.278238976453893</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.296081196916479</v>
+        <v>3.256842135048427</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1157638292511212</v>
+        <v>0.1159468292511212</v>
       </c>
       <c r="C86">
-        <v>0.4477797165482595</v>
+        <v>0.3961984842004584</v>
       </c>
       <c r="D86">
-        <v>4.395099716548259</v>
+        <v>4.391248484200458</v>
       </c>
       <c r="E86">
-        <v>3.81632</v>
+        <v>3.864049999999999</v>
       </c>
       <c r="F86">
-        <v>4.00932</v>
+        <v>4.057049999999999</v>
       </c>
       <c r="G86">
         <v>0.062</v>
@@ -8333,28 +8333,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M86">
-        <v>0.256997412</v>
+        <v>0.260056905</v>
       </c>
       <c r="N86">
-        <v>0.5800025880000002</v>
+        <v>0.5769430950000001</v>
       </c>
       <c r="O86">
         <v>0</v>
       </c>
       <c r="P86">
-        <v>0.5800025880000002</v>
+        <v>0.5769430950000001</v>
       </c>
       <c r="Q86">
-        <v>0.8030025880000001</v>
+        <v>0.799943095</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3869989328195072</v>
+        <v>0.4097455283408077</v>
       </c>
       <c r="T86">
-        <v>5.278238976453889</v>
+        <v>5.630121574884148</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.256842135048427</v>
+        <v>3.218526345224327</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1159468292511212</v>
+        <v>0.1161298292511212</v>
       </c>
       <c r="C87">
-        <v>0.3961984842004584</v>
+        <v>0.3446239952743344</v>
       </c>
       <c r="D87">
-        <v>4.391248484200458</v>
+        <v>4.387403995274334</v>
       </c>
       <c r="E87">
-        <v>3.864049999999999</v>
+        <v>3.91178</v>
       </c>
       <c r="F87">
-        <v>4.057049999999999</v>
+        <v>4.10478</v>
       </c>
       <c r="G87">
         <v>0.062</v>
@@ -8415,28 +8415,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M87">
-        <v>0.260056905</v>
+        <v>0.263116398</v>
       </c>
       <c r="N87">
-        <v>0.5769430950000001</v>
+        <v>0.573883602</v>
       </c>
       <c r="O87">
         <v>0</v>
       </c>
       <c r="P87">
-        <v>0.5769430950000001</v>
+        <v>0.573883602</v>
       </c>
       <c r="Q87">
-        <v>0.799943095</v>
+        <v>0.796883602</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4097455283408077</v>
+        <v>0.4357416375080083</v>
       </c>
       <c r="T87">
-        <v>5.630121574884148</v>
+        <v>6.032273115947302</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.218526345224327</v>
+        <v>3.181101620279858</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1161298292511212</v>
+        <v>0.1163128292511212</v>
       </c>
       <c r="C88">
-        <v>0.3446239952743344</v>
+        <v>0.2930562320740124</v>
       </c>
       <c r="D88">
-        <v>4.387403995274334</v>
+        <v>4.383566232074012</v>
       </c>
       <c r="E88">
-        <v>3.91178</v>
+        <v>3.959509999999999</v>
       </c>
       <c r="F88">
-        <v>4.10478</v>
+        <v>4.152509999999999</v>
       </c>
       <c r="G88">
         <v>0.062</v>
@@ -8497,28 +8497,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M88">
-        <v>0.263116398</v>
+        <v>0.266175891</v>
       </c>
       <c r="N88">
-        <v>0.573883602</v>
+        <v>0.5708241090000001</v>
       </c>
       <c r="O88">
         <v>0</v>
       </c>
       <c r="P88">
-        <v>0.573883602</v>
+        <v>0.5708241090000001</v>
       </c>
       <c r="Q88">
-        <v>0.796883602</v>
+        <v>0.7938241090000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4357416375080083</v>
+        <v>0.4657371480855473</v>
       </c>
       <c r="T88">
-        <v>6.032273115947302</v>
+        <v>6.496294124866325</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.181101620279858</v>
+        <v>3.14453723383986</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1163128292511212</v>
+        <v>0.1164958292511212</v>
       </c>
       <c r="C89">
-        <v>0.2930562320740124</v>
+        <v>0.2414951769654738</v>
       </c>
       <c r="D89">
-        <v>4.383566232074012</v>
+        <v>4.379735176965474</v>
       </c>
       <c r="E89">
-        <v>3.959509999999999</v>
+        <v>4.00724</v>
       </c>
       <c r="F89">
-        <v>4.152509999999999</v>
+        <v>4.20024</v>
       </c>
       <c r="G89">
         <v>0.062</v>
@@ -8579,28 +8579,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M89">
-        <v>0.266175891</v>
+        <v>0.269235384</v>
       </c>
       <c r="N89">
-        <v>0.5708241090000001</v>
+        <v>0.5677646160000001</v>
       </c>
       <c r="O89">
         <v>0</v>
       </c>
       <c r="P89">
-        <v>0.5708241090000001</v>
+        <v>0.5677646160000001</v>
       </c>
       <c r="Q89">
-        <v>0.7938241090000001</v>
+        <v>0.790764616</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4657371480855473</v>
+        <v>0.5007319104260096</v>
       </c>
       <c r="T89">
-        <v>6.496294124866325</v>
+        <v>7.037651968605187</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.14453723383986</v>
+        <v>3.108803856182588</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1164958292511212</v>
+        <v>0.1166788292511212</v>
       </c>
       <c r="C90">
-        <v>0.2414951769654738</v>
+        <v>0.189940812376296</v>
       </c>
       <c r="D90">
-        <v>4.379735176965474</v>
+        <v>4.375910812376295</v>
       </c>
       <c r="E90">
-        <v>4.00724</v>
+        <v>4.05497</v>
       </c>
       <c r="F90">
-        <v>4.20024</v>
+        <v>4.24797</v>
       </c>
       <c r="G90">
         <v>0.062</v>
@@ -8661,28 +8661,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M90">
-        <v>0.269235384</v>
+        <v>0.272294877</v>
       </c>
       <c r="N90">
-        <v>0.5677646160000001</v>
+        <v>0.5647051230000001</v>
       </c>
       <c r="O90">
         <v>0</v>
       </c>
       <c r="P90">
-        <v>0.5677646160000001</v>
+        <v>0.5647051230000001</v>
       </c>
       <c r="Q90">
-        <v>0.790764616</v>
+        <v>0.7877051230000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5007319104260096</v>
+        <v>0.5420893568283742</v>
       </c>
       <c r="T90">
-        <v>7.037651968605187</v>
+        <v>7.677438511205659</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.108803856182588</v>
+        <v>3.073873475776043</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1166788292511212</v>
+        <v>0.1168618292511212</v>
       </c>
       <c r="C91">
-        <v>0.189940812376296</v>
+        <v>0.1383931207953761</v>
       </c>
       <c r="D91">
-        <v>4.375910812376295</v>
+        <v>4.372093120795376</v>
       </c>
       <c r="E91">
-        <v>4.05497</v>
+        <v>4.1027</v>
       </c>
       <c r="F91">
-        <v>4.24797</v>
+        <v>4.2957</v>
       </c>
       <c r="G91">
         <v>0.062</v>
@@ -8743,28 +8743,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M91">
-        <v>0.272294877</v>
+        <v>0.27535437</v>
       </c>
       <c r="N91">
-        <v>0.5647051230000001</v>
+        <v>0.5616456300000001</v>
       </c>
       <c r="O91">
         <v>0</v>
       </c>
       <c r="P91">
-        <v>0.5647051230000001</v>
+        <v>0.5616456300000001</v>
       </c>
       <c r="Q91">
-        <v>0.7877051230000001</v>
+        <v>0.7846456300000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5420893568283742</v>
+        <v>0.5917182925112116</v>
       </c>
       <c r="T91">
-        <v>7.677438511205659</v>
+        <v>8.445182362326225</v>
       </c>
       <c r="U91">
         <v>0.0641</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.073873475776043</v>
+        <v>3.039719326045198</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1168618292511212</v>
+        <v>0.1170448292511212</v>
       </c>
       <c r="C92">
-        <v>0.1383931207953761</v>
+        <v>0.08685208477266926</v>
       </c>
       <c r="D92">
-        <v>4.372093120795376</v>
+        <v>4.368282084772669</v>
       </c>
       <c r="E92">
-        <v>4.1027</v>
+        <v>4.15043</v>
       </c>
       <c r="F92">
-        <v>4.2957</v>
+        <v>4.34343</v>
       </c>
       <c r="G92">
         <v>0.062</v>
@@ -8825,28 +8825,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M92">
-        <v>0.27535437</v>
+        <v>0.278413863</v>
       </c>
       <c r="N92">
-        <v>0.5616456300000001</v>
+        <v>0.558586137</v>
       </c>
       <c r="O92">
         <v>0</v>
       </c>
       <c r="P92">
-        <v>0.5616456300000001</v>
+        <v>0.558586137</v>
       </c>
       <c r="Q92">
-        <v>0.7846456300000001</v>
+        <v>0.781586137</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5917182925112116</v>
+        <v>0.652375880568013</v>
       </c>
       <c r="T92">
-        <v>8.445182362326225</v>
+        <v>9.383535958140252</v>
       </c>
       <c r="U92">
         <v>0.0641</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.039719326045198</v>
+        <v>3.006315816967778</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1170448292511212</v>
+        <v>0.1244038292511212</v>
       </c>
       <c r="C93">
-        <v>0.08685208477266926</v>
+        <v>-0.1088124534261325</v>
       </c>
       <c r="D93">
-        <v>4.368282084772669</v>
+        <v>4.220347546573867</v>
       </c>
       <c r="E93">
-        <v>4.15043</v>
+        <v>4.198160000000001</v>
       </c>
       <c r="F93">
-        <v>4.34343</v>
+        <v>4.39116</v>
       </c>
       <c r="G93">
         <v>0.062</v>
@@ -8907,45 +8907,45 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M93">
-        <v>0.278413863</v>
+        <v>0.315724404</v>
       </c>
       <c r="N93">
-        <v>0.558586137</v>
+        <v>0.5212755960000001</v>
       </c>
       <c r="O93">
         <v>0</v>
       </c>
       <c r="P93">
-        <v>0.558586137</v>
+        <v>0.5212755960000001</v>
       </c>
       <c r="Q93">
-        <v>0.781586137</v>
+        <v>0.744275596</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.652375880568013</v>
+        <v>0.7281978656390148</v>
       </c>
       <c r="T93">
-        <v>9.383535958140252</v>
+        <v>10.55647795290779</v>
       </c>
       <c r="U93">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V93">
         <v>0</v>
       </c>
       <c r="W93">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y93">
-        <v>3.006315816967778</v>
+        <v>2.651046258685787</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1244038292511212</v>
+        <v>0.1246648292511212</v>
       </c>
       <c r="C94">
-        <v>-0.1088124534261325</v>
+        <v>-0.161605448515413</v>
       </c>
       <c r="D94">
-        <v>4.220347546573867</v>
+        <v>4.215284551484586</v>
       </c>
       <c r="E94">
-        <v>4.198160000000001</v>
+        <v>4.24589</v>
       </c>
       <c r="F94">
-        <v>4.39116</v>
+        <v>4.43889</v>
       </c>
       <c r="G94">
         <v>0.062</v>
@@ -8989,28 +8989,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M94">
-        <v>0.315724404</v>
+        <v>0.319156191</v>
       </c>
       <c r="N94">
-        <v>0.5212755960000001</v>
+        <v>0.517843809</v>
       </c>
       <c r="O94">
         <v>0</v>
       </c>
       <c r="P94">
-        <v>0.5212755960000001</v>
+        <v>0.517843809</v>
       </c>
       <c r="Q94">
-        <v>0.744275596</v>
+        <v>0.740843809</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7281978656390148</v>
+        <v>0.825683275016017</v>
       </c>
       <c r="T94">
-        <v>10.55647795290779</v>
+        <v>12.06454623189461</v>
       </c>
       <c r="U94">
         <v>0.07190000000000001</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.651046258685787</v>
+        <v>2.622540384936478</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1246648292511212</v>
+        <v>0.1249258292511212</v>
       </c>
       <c r="C95">
-        <v>-0.161605448515413</v>
+        <v>-0.2143863103840182</v>
       </c>
       <c r="D95">
-        <v>4.215284551484586</v>
+        <v>4.210233689615982</v>
       </c>
       <c r="E95">
-        <v>4.24589</v>
+        <v>4.293620000000001</v>
       </c>
       <c r="F95">
-        <v>4.43889</v>
+        <v>4.48662</v>
       </c>
       <c r="G95">
         <v>0.062</v>
@@ -9071,28 +9071,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M95">
-        <v>0.319156191</v>
+        <v>0.3225879780000001</v>
       </c>
       <c r="N95">
-        <v>0.517843809</v>
+        <v>0.514412022</v>
       </c>
       <c r="O95">
         <v>0</v>
       </c>
       <c r="P95">
-        <v>0.517843809</v>
+        <v>0.514412022</v>
       </c>
       <c r="Q95">
-        <v>0.740843809</v>
+        <v>0.737412022</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.825683275016017</v>
+        <v>0.9556638208520201</v>
       </c>
       <c r="T95">
-        <v>12.06454623189461</v>
+        <v>14.07530393721039</v>
       </c>
       <c r="U95">
         <v>0.07190000000000001</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.622540384936478</v>
+        <v>2.594641019139281</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1249258292511212</v>
+        <v>0.1251868292511212</v>
       </c>
       <c r="C96">
-        <v>-0.2143863103840182</v>
+        <v>-0.2671550825947566</v>
       </c>
       <c r="D96">
-        <v>4.210233689615982</v>
+        <v>4.205194917405243</v>
       </c>
       <c r="E96">
-        <v>4.293620000000001</v>
+        <v>4.34135</v>
       </c>
       <c r="F96">
-        <v>4.48662</v>
+        <v>4.53435</v>
       </c>
       <c r="G96">
         <v>0.062</v>
@@ -9153,28 +9153,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M96">
-        <v>0.3225879780000001</v>
+        <v>0.326019765</v>
       </c>
       <c r="N96">
-        <v>0.514412022</v>
+        <v>0.5109802350000001</v>
       </c>
       <c r="O96">
         <v>0</v>
       </c>
       <c r="P96">
-        <v>0.514412022</v>
+        <v>0.5109802350000001</v>
       </c>
       <c r="Q96">
-        <v>0.737412022</v>
+        <v>0.7339802350000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9556638208520201</v>
+        <v>1.137636585022425</v>
       </c>
       <c r="T96">
-        <v>14.07530393721039</v>
+        <v>16.89036472465247</v>
       </c>
       <c r="U96">
         <v>0.07190000000000001</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.594641019139281</v>
+        <v>2.567329008411499</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1251868292511212</v>
+        <v>0.1254478292511212</v>
       </c>
       <c r="C97">
-        <v>-0.2671550825947566</v>
+        <v>-0.3199118085021437</v>
       </c>
       <c r="D97">
-        <v>4.205194917405243</v>
+        <v>4.200168191497856</v>
       </c>
       <c r="E97">
-        <v>4.34135</v>
+        <v>4.389080000000001</v>
       </c>
       <c r="F97">
-        <v>4.53435</v>
+        <v>4.58208</v>
       </c>
       <c r="G97">
         <v>0.062</v>
@@ -9235,28 +9235,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M97">
-        <v>0.326019765</v>
+        <v>0.329451552</v>
       </c>
       <c r="N97">
-        <v>0.5109802350000001</v>
+        <v>0.5075484480000001</v>
       </c>
       <c r="O97">
         <v>0</v>
       </c>
       <c r="P97">
-        <v>0.5109802350000001</v>
+        <v>0.5075484480000001</v>
       </c>
       <c r="Q97">
-        <v>0.7339802350000001</v>
+        <v>0.7305484480000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.137636585022425</v>
+        <v>1.410595731278031</v>
       </c>
       <c r="T97">
-        <v>16.89036472465247</v>
+        <v>21.1129559058156</v>
       </c>
       <c r="U97">
         <v>0.07190000000000001</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.567329008411499</v>
+        <v>2.540585997907213</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1254478292511212</v>
+        <v>0.1257088292511211</v>
       </c>
       <c r="C98">
-        <v>-0.3199118085021428</v>
+        <v>-0.3726565312536438</v>
       </c>
       <c r="D98">
-        <v>4.200168191497856</v>
+        <v>4.195153468746356</v>
       </c>
       <c r="E98">
-        <v>4.38908</v>
+        <v>4.43681</v>
       </c>
       <c r="F98">
-        <v>4.582079999999999</v>
+        <v>4.62981</v>
       </c>
       <c r="G98">
         <v>0.062</v>
@@ -9317,28 +9317,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M98">
-        <v>0.329451552</v>
+        <v>0.332883339</v>
       </c>
       <c r="N98">
-        <v>0.5075484480000001</v>
+        <v>0.5041166610000001</v>
       </c>
       <c r="O98">
         <v>0</v>
       </c>
       <c r="P98">
-        <v>0.5075484480000001</v>
+        <v>0.5041166610000001</v>
       </c>
       <c r="Q98">
-        <v>0.7305484480000001</v>
+        <v>0.7271166610000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.410595731278028</v>
+        <v>1.865527641704037</v>
       </c>
       <c r="T98">
-        <v>21.11295590581554</v>
+        <v>28.15060787442072</v>
       </c>
       <c r="U98">
         <v>0.07190000000000001</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.540585997907213</v>
+        <v>2.514394389681366</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1257088292511211</v>
+        <v>0.1297918292511211</v>
       </c>
       <c r="C99">
-        <v>-0.3726565312536438</v>
+        <v>-0.4973049328006276</v>
       </c>
       <c r="D99">
-        <v>4.195153468746356</v>
+        <v>4.118235067199372</v>
       </c>
       <c r="E99">
-        <v>4.43681</v>
+        <v>4.48454</v>
       </c>
       <c r="F99">
-        <v>4.62981</v>
+        <v>4.67754</v>
       </c>
       <c r="G99">
         <v>0.062</v>
@@ -9399,45 +9399,45 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M99">
-        <v>0.332883339</v>
+        <v>0.354557532</v>
       </c>
       <c r="N99">
-        <v>0.5041166610000001</v>
+        <v>0.4824424680000001</v>
       </c>
       <c r="O99">
         <v>0</v>
       </c>
       <c r="P99">
-        <v>0.5041166610000001</v>
+        <v>0.4824424680000001</v>
       </c>
       <c r="Q99">
-        <v>0.7271166610000001</v>
+        <v>0.7054424680000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.865527641704037</v>
+        <v>2.775391462556055</v>
       </c>
       <c r="T99">
-        <v>28.15060787442072</v>
+        <v>42.22591181163108</v>
       </c>
       <c r="U99">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V99">
         <v>0</v>
       </c>
       <c r="W99">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y99">
-        <v>2.514394389681366</v>
+        <v>2.360688814812712</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1297918292511211</v>
+        <v>0.1300918292511212</v>
       </c>
       <c r="C100">
-        <v>-0.4973049328006276</v>
+        <v>-0.5505754553583069</v>
       </c>
       <c r="D100">
-        <v>4.118235067199372</v>
+        <v>4.112694544641693</v>
       </c>
       <c r="E100">
-        <v>4.48454</v>
+        <v>4.53227</v>
       </c>
       <c r="F100">
-        <v>4.67754</v>
+        <v>4.72527</v>
       </c>
       <c r="G100">
         <v>0.062</v>
@@ -9481,28 +9481,28 @@
         <v>0.8370000000000001</v>
       </c>
       <c r="M100">
-        <v>0.354557532</v>
+        <v>0.3581754660000001</v>
       </c>
       <c r="N100">
-        <v>0.4824424680000001</v>
+        <v>0.478824534</v>
       </c>
       <c r="O100">
         <v>0</v>
       </c>
       <c r="P100">
-        <v>0.4824424680000001</v>
+        <v>0.478824534</v>
       </c>
       <c r="Q100">
-        <v>0.7054424680000001</v>
+        <v>0.701824534</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.775391462556055</v>
+        <v>5.504982925112111</v>
       </c>
       <c r="T100">
-        <v>42.22591181163108</v>
+        <v>84.45182362326216</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.360688814812712</v>
+        <v>2.336843473248947</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1300918292511212</v>
-      </c>
-      <c r="C101">
-        <v>-0.5505754553583069</v>
-      </c>
-      <c r="D101">
-        <v>4.112694544641693</v>
-      </c>
-      <c r="E101">
-        <v>4.53227</v>
-      </c>
-      <c r="F101">
-        <v>4.72527</v>
-      </c>
-      <c r="G101">
-        <v>0.062</v>
-      </c>
-      <c r="H101">
-        <v>4.58</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.06</v>
-      </c>
-      <c r="K101">
-        <v>0.223</v>
-      </c>
-      <c r="L101">
-        <v>0.8370000000000001</v>
-      </c>
-      <c r="M101">
-        <v>0.3581754660000001</v>
-      </c>
-      <c r="N101">
-        <v>0.478824534</v>
-      </c>
-      <c r="O101">
-        <v>0</v>
-      </c>
-      <c r="P101">
-        <v>0.478824534</v>
-      </c>
-      <c r="Q101">
-        <v>0.701824534</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.504982925112111</v>
-      </c>
-      <c r="T101">
-        <v>84.45182362326216</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.336843473248947</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
